--- a/LTD_DISPLAY_CPU3/readme/LTD故障代码表.xlsx
+++ b/LTD_DISPLAY_CPU3/readme/LTD故障代码表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="4"/>
+    <workbookView windowHeight="17655" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="总表" sheetId="1" r:id="rId1"/>
@@ -12,6 +12,7 @@
     <sheet name="测量结果" sheetId="2" r:id="rId3"/>
     <sheet name="保持寄存器表显示" sheetId="5" state="hidden" r:id="rId4"/>
     <sheet name="保持寄存器显示" sheetId="6" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3206" uniqueCount="893">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5466" uniqueCount="1092">
   <si>
     <t>故障类型</t>
   </si>
@@ -2710,6 +2711,603 @@
   </si>
   <si>
     <t>(uint8_t*)"C3Proto"},</t>
+  </si>
+  <si>
+    <t>// 字段顺序：名称\t数值\t数据号\t起始地址\t寄存器数\t是否检范围\t最小\t最大\t单位\t小数\t偏移\t写权\t类型\t显示\t隐藏\t英文</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"故障自动回零",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_ERROR_AUTO_BACK_ZERO,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_ERROR_AUTO_BACK_ZERO,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"ErrAutoBackZero"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"故障停止测量",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_ERROR_STOP_MEASUREMENT,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_ERROR_STOP_MEASUREMENT,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"ErrStopMeas"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留1",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED1,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED1,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv1"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留2",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED2,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED2,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv2"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留3",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED3,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED3,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv3"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留4",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED4,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED4,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv4"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留5",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED5,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED5,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv5"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留6",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED6,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED6,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv6"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留7",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED7,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED7,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv7"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留8",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED8,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED8,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv8"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留9",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED9,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED9,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv9"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"零点阈值比例",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_ZERO_WEIGHT_THRESHOLD_RATIO,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_ZERO_WEIGHT_THRESHOLD_RATIO,</t>
+  </si>
+  <si>
+    <t>100,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"ZeroThRatio"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"称重忽略区",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_WEIGHT_IGNORE_ZONE,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_WEIGHT_IGNORE_ZONE,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"WeightIgnore"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"零点最大偏差",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_MAX_ZERO_DEVIATION_DISTANCE,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_MAX_ZERO_DEVIATION_DISTANCE,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"MaxZeroDev"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留10",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED10,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED10,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv10"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留11",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED11,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED11,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv11"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"液位探头距差",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_LIQUID_SENSOR_DISTANCE_DIFF,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_LIQUID_SENSOR_DISTANCE_DIFF,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"LvlSenDiff"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留12",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED12,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED12,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv12"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留13",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED13,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED13,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv13"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"水罐高",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_WATER_TANK_HEIGHT,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_WATER_TANK_HEIGHT,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"WaterTankH"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"水位探头距差",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_WATER_LEVEL_SENSOR_DISTANCE_DIFF,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_WATER_LEVEL_SENSOR_DISTANCE_DIFF,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"WaterSenDiff"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"水位电容阈值",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_WATER_CAP_THRESHOLD,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_WATER_CAP_THRESHOLD,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"WaterCapTh"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"水位电容滞回",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_WATER_CAP_HYSTERESIS,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_WATER_CAP_HYSTERESIS,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"WaterCapHys"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留14",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED14,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED14,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv14"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留15",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED15,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED15,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv15"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"罐底检测模式",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_BOTTOM_DETECT_MODE,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_BOTTOM_DETECT_MODE,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"BottomMode"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"罐底角度阈值",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_BOTTOM_ANGLE_THRESHOLD,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_BOTTOM_ANGLE_THRESHOLD,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"BottomAngTh"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"罐底称重阈值",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_BOTTOM_WEIGHT_THRESHOLD,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_BOTTOM_WEIGHT_THRESHOLD,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"BottomWtTh"},</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_REFRESH_TANKHEIGHT_FLAG,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_REFRESH_TANKHEIGHT_FLAG,</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_MAX_TANKHEIGHT_DEVIATION,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_MAX_TANKHEIGHT_DEVIATION,</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_INITIAL_TANKHEIGHT,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_INITIAL_TANKHEIGHT,</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_CURRENT_TANKHEIGHT,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_CURRENT_TANKHEIGHT,</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留16",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED16,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED16,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv16"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留17",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED17,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED17,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv17"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留18",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED18,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED18,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv18"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留19",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED19,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED19,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv19"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"区间上限",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_INTERVAL_TOPLIMIT,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_INTERVAL_TOPLIMIT,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"IntTop"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"区间下限",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_INTERVAL_BOTTOMLIMIT,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_INTERVAL_BOTTOMLIMIT,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"IntBottom"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留20",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED20,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED20,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv20"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留21",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED21,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED21,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv21"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"密度上限",</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"密度下限",</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"密度步进",</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"最高点距液面",</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留22",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED22,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED22,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv22"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留23",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED23,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED23,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv23"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留24",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED24,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED24,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv24"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留25",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED25,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED25,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv25"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留26",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED26,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED26,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv26"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留27",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED27,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED27,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv27"},</t>
+  </si>
+  <si>
+    <t>COM_NUM_CALIBRATE_WATER,</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"密度分布液位",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_DENSITY_DISTRIBUTION_OIL_LEVEL,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"DistOilLvl"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"电机运行距离",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_MOTOR_COMMAND_DISTANCE,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"MotorDist"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留28",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED28,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED28,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv28"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"保留29",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_RESERVED29,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_RESERVED29,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"Rsv29"},</t>
+  </si>
+  <si>
+    <t>/* ==================== CPU3 本机参数（保持你原来的寄存器宏）==================== */</t>
+  </si>
+  <si>
+    <t>ret_arr_word,</t>
   </si>
 </sst>
 </file>
@@ -14969,4 +15567,7091 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A2:Q168"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="1" width="58.75" customWidth="1"/>
+    <col min="2" max="2" width="109.375" customWidth="1"/>
+    <col min="5" max="5" width="60.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:17">
+      <c r="A2" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="B4" t="s">
+        <v>435</v>
+      </c>
+      <c r="C4" t="s">
+        <v>436</v>
+      </c>
+      <c r="D4" t="s">
+        <v>437</v>
+      </c>
+      <c r="E4" t="s">
+        <v>438</v>
+      </c>
+      <c r="F4" t="s">
+        <v>439</v>
+      </c>
+      <c r="G4" t="s">
+        <v>440</v>
+      </c>
+      <c r="H4" t="s">
+        <v>436</v>
+      </c>
+      <c r="I4" t="s">
+        <v>436</v>
+      </c>
+      <c r="J4" t="s">
+        <v>441</v>
+      </c>
+      <c r="K4" t="s">
+        <v>436</v>
+      </c>
+      <c r="L4" t="s">
+        <v>436</v>
+      </c>
+      <c r="M4" t="s">
+        <v>442</v>
+      </c>
+      <c r="N4" t="s">
+        <v>443</v>
+      </c>
+      <c r="O4" t="s">
+        <v>444</v>
+      </c>
+      <c r="P4" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="B6" t="s">
+        <v>467</v>
+      </c>
+      <c r="C6" t="s">
+        <v>436</v>
+      </c>
+      <c r="D6" t="s">
+        <v>468</v>
+      </c>
+      <c r="E6" t="s">
+        <v>469</v>
+      </c>
+      <c r="F6" t="s">
+        <v>439</v>
+      </c>
+      <c r="G6" t="s">
+        <v>440</v>
+      </c>
+      <c r="H6" t="s">
+        <v>436</v>
+      </c>
+      <c r="I6" t="s">
+        <v>436</v>
+      </c>
+      <c r="J6" t="s">
+        <v>441</v>
+      </c>
+      <c r="K6" t="s">
+        <v>436</v>
+      </c>
+      <c r="L6" t="s">
+        <v>436</v>
+      </c>
+      <c r="M6" t="s">
+        <v>440</v>
+      </c>
+      <c r="N6" t="s">
+        <v>443</v>
+      </c>
+      <c r="O6" t="s">
+        <v>465</v>
+      </c>
+      <c r="P6" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="B7" t="s">
+        <v>471</v>
+      </c>
+      <c r="C7" t="s">
+        <v>436</v>
+      </c>
+      <c r="D7" t="s">
+        <v>472</v>
+      </c>
+      <c r="E7" t="s">
+        <v>473</v>
+      </c>
+      <c r="F7" t="s">
+        <v>439</v>
+      </c>
+      <c r="G7" t="s">
+        <v>440</v>
+      </c>
+      <c r="H7" t="s">
+        <v>436</v>
+      </c>
+      <c r="I7" t="s">
+        <v>436</v>
+      </c>
+      <c r="J7" t="s">
+        <v>441</v>
+      </c>
+      <c r="K7" t="s">
+        <v>436</v>
+      </c>
+      <c r="L7" t="s">
+        <v>436</v>
+      </c>
+      <c r="M7" t="s">
+        <v>440</v>
+      </c>
+      <c r="N7" t="s">
+        <v>443</v>
+      </c>
+      <c r="O7" t="s">
+        <v>444</v>
+      </c>
+      <c r="P7" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="B8" t="s">
+        <v>719</v>
+      </c>
+      <c r="C8" t="s">
+        <v>436</v>
+      </c>
+      <c r="D8" t="s">
+        <v>720</v>
+      </c>
+      <c r="E8" t="s">
+        <v>721</v>
+      </c>
+      <c r="F8" t="s">
+        <v>439</v>
+      </c>
+      <c r="G8" t="s">
+        <v>440</v>
+      </c>
+      <c r="H8" t="s">
+        <v>436</v>
+      </c>
+      <c r="I8" t="s">
+        <v>436</v>
+      </c>
+      <c r="J8" t="s">
+        <v>441</v>
+      </c>
+      <c r="K8" t="s">
+        <v>465</v>
+      </c>
+      <c r="L8" t="s">
+        <v>436</v>
+      </c>
+      <c r="M8" t="s">
+        <v>440</v>
+      </c>
+      <c r="N8" t="s">
+        <v>443</v>
+      </c>
+      <c r="O8" t="s">
+        <v>562</v>
+      </c>
+      <c r="P8" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="B9" t="s">
+        <v>475</v>
+      </c>
+      <c r="C9" t="s">
+        <v>436</v>
+      </c>
+      <c r="D9" t="s">
+        <v>476</v>
+      </c>
+      <c r="E9" t="s">
+        <v>477</v>
+      </c>
+      <c r="F9" t="s">
+        <v>439</v>
+      </c>
+      <c r="G9" t="s">
+        <v>440</v>
+      </c>
+      <c r="H9" t="s">
+        <v>436</v>
+      </c>
+      <c r="I9" t="s">
+        <v>436</v>
+      </c>
+      <c r="J9" t="s">
+        <v>441</v>
+      </c>
+      <c r="K9" t="s">
+        <v>465</v>
+      </c>
+      <c r="L9" t="s">
+        <v>436</v>
+      </c>
+      <c r="M9" t="s">
+        <v>440</v>
+      </c>
+      <c r="N9" t="s">
+        <v>443</v>
+      </c>
+      <c r="O9" t="s">
+        <v>451</v>
+      </c>
+      <c r="P9" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="B10" t="s">
+        <v>724</v>
+      </c>
+      <c r="C10" t="s">
+        <v>436</v>
+      </c>
+      <c r="D10" t="s">
+        <v>725</v>
+      </c>
+      <c r="E10" t="s">
+        <v>726</v>
+      </c>
+      <c r="F10" t="s">
+        <v>439</v>
+      </c>
+      <c r="G10" t="s">
+        <v>440</v>
+      </c>
+      <c r="H10" t="s">
+        <v>436</v>
+      </c>
+      <c r="I10" t="s">
+        <v>436</v>
+      </c>
+      <c r="J10" t="s">
+        <v>441</v>
+      </c>
+      <c r="K10" t="s">
+        <v>436</v>
+      </c>
+      <c r="L10" t="s">
+        <v>436</v>
+      </c>
+      <c r="M10" t="s">
+        <v>442</v>
+      </c>
+      <c r="N10" t="s">
+        <v>443</v>
+      </c>
+      <c r="O10" t="s">
+        <v>465</v>
+      </c>
+      <c r="P10" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="B11" t="s">
+        <v>894</v>
+      </c>
+      <c r="C11" t="s">
+        <v>436</v>
+      </c>
+      <c r="D11" t="s">
+        <v>895</v>
+      </c>
+      <c r="E11" t="s">
+        <v>896</v>
+      </c>
+      <c r="F11" t="s">
+        <v>439</v>
+      </c>
+      <c r="G11" t="s">
+        <v>442</v>
+      </c>
+      <c r="H11" t="s">
+        <v>436</v>
+      </c>
+      <c r="I11" t="s">
+        <v>450</v>
+      </c>
+      <c r="J11" t="s">
+        <v>441</v>
+      </c>
+      <c r="K11" t="s">
+        <v>436</v>
+      </c>
+      <c r="L11" t="s">
+        <v>436</v>
+      </c>
+      <c r="M11" t="s">
+        <v>442</v>
+      </c>
+      <c r="N11" t="s">
+        <v>443</v>
+      </c>
+      <c r="O11" t="s">
+        <v>450</v>
+      </c>
+      <c r="P11" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="B12" t="s">
+        <v>898</v>
+      </c>
+      <c r="C12" t="s">
+        <v>436</v>
+      </c>
+      <c r="D12" t="s">
+        <v>899</v>
+      </c>
+      <c r="E12" t="s">
+        <v>900</v>
+      </c>
+      <c r="F12" t="s">
+        <v>439</v>
+      </c>
+      <c r="G12" t="s">
+        <v>442</v>
+      </c>
+      <c r="H12" t="s">
+        <v>436</v>
+      </c>
+      <c r="I12" t="s">
+        <v>450</v>
+      </c>
+      <c r="J12" t="s">
+        <v>441</v>
+      </c>
+      <c r="K12" t="s">
+        <v>436</v>
+      </c>
+      <c r="L12" t="s">
+        <v>436</v>
+      </c>
+      <c r="M12" t="s">
+        <v>442</v>
+      </c>
+      <c r="N12" t="s">
+        <v>443</v>
+      </c>
+      <c r="O12" t="s">
+        <v>450</v>
+      </c>
+      <c r="P12" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="B14" t="s">
+        <v>902</v>
+      </c>
+      <c r="C14" t="s">
+        <v>436</v>
+      </c>
+      <c r="D14" t="s">
+        <v>903</v>
+      </c>
+      <c r="E14" t="s">
+        <v>904</v>
+      </c>
+      <c r="F14" t="s">
+        <v>439</v>
+      </c>
+      <c r="G14" t="s">
+        <v>440</v>
+      </c>
+      <c r="H14" t="s">
+        <v>436</v>
+      </c>
+      <c r="I14" t="s">
+        <v>436</v>
+      </c>
+      <c r="J14" t="s">
+        <v>441</v>
+      </c>
+      <c r="K14" t="s">
+        <v>436</v>
+      </c>
+      <c r="L14" t="s">
+        <v>436</v>
+      </c>
+      <c r="M14" t="s">
+        <v>440</v>
+      </c>
+      <c r="N14" t="s">
+        <v>443</v>
+      </c>
+      <c r="O14" t="s">
+        <v>444</v>
+      </c>
+      <c r="P14" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="B15" t="s">
+        <v>906</v>
+      </c>
+      <c r="C15" t="s">
+        <v>436</v>
+      </c>
+      <c r="D15" t="s">
+        <v>907</v>
+      </c>
+      <c r="E15" t="s">
+        <v>908</v>
+      </c>
+      <c r="F15" t="s">
+        <v>439</v>
+      </c>
+      <c r="G15" t="s">
+        <v>440</v>
+      </c>
+      <c r="H15" t="s">
+        <v>436</v>
+      </c>
+      <c r="I15" t="s">
+        <v>436</v>
+      </c>
+      <c r="J15" t="s">
+        <v>441</v>
+      </c>
+      <c r="K15" t="s">
+        <v>436</v>
+      </c>
+      <c r="L15" t="s">
+        <v>436</v>
+      </c>
+      <c r="M15" t="s">
+        <v>440</v>
+      </c>
+      <c r="N15" t="s">
+        <v>443</v>
+      </c>
+      <c r="O15" t="s">
+        <v>444</v>
+      </c>
+      <c r="P15" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="B16" t="s">
+        <v>910</v>
+      </c>
+      <c r="C16" t="s">
+        <v>436</v>
+      </c>
+      <c r="D16" t="s">
+        <v>911</v>
+      </c>
+      <c r="E16" t="s">
+        <v>912</v>
+      </c>
+      <c r="F16" t="s">
+        <v>439</v>
+      </c>
+      <c r="G16" t="s">
+        <v>440</v>
+      </c>
+      <c r="H16" t="s">
+        <v>436</v>
+      </c>
+      <c r="I16" t="s">
+        <v>436</v>
+      </c>
+      <c r="J16" t="s">
+        <v>441</v>
+      </c>
+      <c r="K16" t="s">
+        <v>436</v>
+      </c>
+      <c r="L16" t="s">
+        <v>436</v>
+      </c>
+      <c r="M16" t="s">
+        <v>440</v>
+      </c>
+      <c r="N16" t="s">
+        <v>443</v>
+      </c>
+      <c r="O16" t="s">
+        <v>444</v>
+      </c>
+      <c r="P16" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17">
+      <c r="B17" t="s">
+        <v>914</v>
+      </c>
+      <c r="C17" t="s">
+        <v>436</v>
+      </c>
+      <c r="D17" t="s">
+        <v>915</v>
+      </c>
+      <c r="E17" t="s">
+        <v>916</v>
+      </c>
+      <c r="F17" t="s">
+        <v>439</v>
+      </c>
+      <c r="G17" t="s">
+        <v>440</v>
+      </c>
+      <c r="H17" t="s">
+        <v>436</v>
+      </c>
+      <c r="I17" t="s">
+        <v>436</v>
+      </c>
+      <c r="J17" t="s">
+        <v>441</v>
+      </c>
+      <c r="K17" t="s">
+        <v>436</v>
+      </c>
+      <c r="L17" t="s">
+        <v>436</v>
+      </c>
+      <c r="M17" t="s">
+        <v>440</v>
+      </c>
+      <c r="N17" t="s">
+        <v>443</v>
+      </c>
+      <c r="O17" t="s">
+        <v>444</v>
+      </c>
+      <c r="P17" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17">
+      <c r="B18" t="s">
+        <v>918</v>
+      </c>
+      <c r="C18" t="s">
+        <v>436</v>
+      </c>
+      <c r="D18" t="s">
+        <v>919</v>
+      </c>
+      <c r="E18" t="s">
+        <v>920</v>
+      </c>
+      <c r="F18" t="s">
+        <v>439</v>
+      </c>
+      <c r="G18" t="s">
+        <v>440</v>
+      </c>
+      <c r="H18" t="s">
+        <v>436</v>
+      </c>
+      <c r="I18" t="s">
+        <v>436</v>
+      </c>
+      <c r="J18" t="s">
+        <v>441</v>
+      </c>
+      <c r="K18" t="s">
+        <v>436</v>
+      </c>
+      <c r="L18" t="s">
+        <v>436</v>
+      </c>
+      <c r="M18" t="s">
+        <v>440</v>
+      </c>
+      <c r="N18" t="s">
+        <v>443</v>
+      </c>
+      <c r="O18" t="s">
+        <v>444</v>
+      </c>
+      <c r="P18" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17">
+      <c r="B20" t="s">
+        <v>462</v>
+      </c>
+      <c r="C20" t="s">
+        <v>436</v>
+      </c>
+      <c r="D20" t="s">
+        <v>463</v>
+      </c>
+      <c r="E20" t="s">
+        <v>464</v>
+      </c>
+      <c r="F20" t="s">
+        <v>439</v>
+      </c>
+      <c r="G20" t="s">
+        <v>440</v>
+      </c>
+      <c r="H20" t="s">
+        <v>436</v>
+      </c>
+      <c r="I20" t="s">
+        <v>436</v>
+      </c>
+      <c r="J20" t="s">
+        <v>441</v>
+      </c>
+      <c r="K20" t="s">
+        <v>465</v>
+      </c>
+      <c r="L20" t="s">
+        <v>436</v>
+      </c>
+      <c r="M20" t="s">
+        <v>442</v>
+      </c>
+      <c r="N20" t="s">
+        <v>443</v>
+      </c>
+      <c r="O20" t="s">
+        <v>456</v>
+      </c>
+      <c r="P20" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17">
+      <c r="B21" t="s">
+        <v>706</v>
+      </c>
+      <c r="C21" t="s">
+        <v>436</v>
+      </c>
+      <c r="D21" t="s">
+        <v>707</v>
+      </c>
+      <c r="E21" t="s">
+        <v>708</v>
+      </c>
+      <c r="F21" t="s">
+        <v>439</v>
+      </c>
+      <c r="G21" t="s">
+        <v>440</v>
+      </c>
+      <c r="H21" t="s">
+        <v>436</v>
+      </c>
+      <c r="I21" t="s">
+        <v>436</v>
+      </c>
+      <c r="J21" t="s">
+        <v>441</v>
+      </c>
+      <c r="K21" t="s">
+        <v>439</v>
+      </c>
+      <c r="L21" t="s">
+        <v>436</v>
+      </c>
+      <c r="M21" t="s">
+        <v>442</v>
+      </c>
+      <c r="N21" t="s">
+        <v>443</v>
+      </c>
+      <c r="O21" t="s">
+        <v>465</v>
+      </c>
+      <c r="P21" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17">
+      <c r="B22" t="s">
+        <v>710</v>
+      </c>
+      <c r="C22" t="s">
+        <v>436</v>
+      </c>
+      <c r="D22" t="s">
+        <v>711</v>
+      </c>
+      <c r="E22" t="s">
+        <v>712</v>
+      </c>
+      <c r="F22" t="s">
+        <v>439</v>
+      </c>
+      <c r="G22" t="s">
+        <v>440</v>
+      </c>
+      <c r="H22" t="s">
+        <v>436</v>
+      </c>
+      <c r="I22" t="s">
+        <v>436</v>
+      </c>
+      <c r="J22" t="s">
+        <v>441</v>
+      </c>
+      <c r="K22" t="s">
+        <v>450</v>
+      </c>
+      <c r="L22" t="s">
+        <v>436</v>
+      </c>
+      <c r="M22" t="s">
+        <v>442</v>
+      </c>
+      <c r="N22" t="s">
+        <v>443</v>
+      </c>
+      <c r="O22" t="s">
+        <v>555</v>
+      </c>
+      <c r="P22" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17">
+      <c r="B23" t="s">
+        <v>714</v>
+      </c>
+      <c r="C23" t="s">
+        <v>436</v>
+      </c>
+      <c r="D23" t="s">
+        <v>715</v>
+      </c>
+      <c r="E23" t="s">
+        <v>716</v>
+      </c>
+      <c r="F23" t="s">
+        <v>439</v>
+      </c>
+      <c r="G23" t="s">
+        <v>440</v>
+      </c>
+      <c r="H23" t="s">
+        <v>436</v>
+      </c>
+      <c r="I23" t="s">
+        <v>436</v>
+      </c>
+      <c r="J23" t="s">
+        <v>441</v>
+      </c>
+      <c r="K23" t="s">
+        <v>465</v>
+      </c>
+      <c r="L23" t="s">
+        <v>436</v>
+      </c>
+      <c r="M23" t="s">
+        <v>442</v>
+      </c>
+      <c r="N23" t="s">
+        <v>443</v>
+      </c>
+      <c r="O23" t="s">
+        <v>456</v>
+      </c>
+      <c r="P23" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17">
+      <c r="B24" t="s">
+        <v>922</v>
+      </c>
+      <c r="C24" t="s">
+        <v>436</v>
+      </c>
+      <c r="D24" t="s">
+        <v>923</v>
+      </c>
+      <c r="E24" t="s">
+        <v>924</v>
+      </c>
+      <c r="F24" t="s">
+        <v>439</v>
+      </c>
+      <c r="G24" t="s">
+        <v>440</v>
+      </c>
+      <c r="H24" t="s">
+        <v>436</v>
+      </c>
+      <c r="I24" t="s">
+        <v>436</v>
+      </c>
+      <c r="J24" t="s">
+        <v>441</v>
+      </c>
+      <c r="K24" t="s">
+        <v>436</v>
+      </c>
+      <c r="L24" t="s">
+        <v>436</v>
+      </c>
+      <c r="M24" t="s">
+        <v>440</v>
+      </c>
+      <c r="N24" t="s">
+        <v>443</v>
+      </c>
+      <c r="O24" t="s">
+        <v>444</v>
+      </c>
+      <c r="P24" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17">
+      <c r="B25" t="s">
+        <v>926</v>
+      </c>
+      <c r="C25" t="s">
+        <v>436</v>
+      </c>
+      <c r="D25" t="s">
+        <v>927</v>
+      </c>
+      <c r="E25" t="s">
+        <v>928</v>
+      </c>
+      <c r="F25" t="s">
+        <v>439</v>
+      </c>
+      <c r="G25" t="s">
+        <v>440</v>
+      </c>
+      <c r="H25" t="s">
+        <v>436</v>
+      </c>
+      <c r="I25" t="s">
+        <v>436</v>
+      </c>
+      <c r="J25" t="s">
+        <v>441</v>
+      </c>
+      <c r="K25" t="s">
+        <v>436</v>
+      </c>
+      <c r="L25" t="s">
+        <v>436</v>
+      </c>
+      <c r="M25" t="s">
+        <v>440</v>
+      </c>
+      <c r="N25" t="s">
+        <v>443</v>
+      </c>
+      <c r="O25" t="s">
+        <v>444</v>
+      </c>
+      <c r="P25" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17">
+      <c r="B27" t="s">
+        <v>728</v>
+      </c>
+      <c r="C27" t="s">
+        <v>436</v>
+      </c>
+      <c r="D27" t="s">
+        <v>481</v>
+      </c>
+      <c r="E27" t="s">
+        <v>482</v>
+      </c>
+      <c r="F27" t="s">
+        <v>439</v>
+      </c>
+      <c r="G27" t="s">
+        <v>440</v>
+      </c>
+      <c r="H27" t="s">
+        <v>436</v>
+      </c>
+      <c r="I27" t="s">
+        <v>436</v>
+      </c>
+      <c r="J27" t="s">
+        <v>441</v>
+      </c>
+      <c r="K27" t="s">
+        <v>436</v>
+      </c>
+      <c r="L27" t="s">
+        <v>436</v>
+      </c>
+      <c r="M27" t="s">
+        <v>442</v>
+      </c>
+      <c r="N27" t="s">
+        <v>443</v>
+      </c>
+      <c r="O27" t="s">
+        <v>451</v>
+      </c>
+      <c r="P27" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17">
+      <c r="B28" t="s">
+        <v>730</v>
+      </c>
+      <c r="C28" t="s">
+        <v>436</v>
+      </c>
+      <c r="D28" t="s">
+        <v>498</v>
+      </c>
+      <c r="E28" t="s">
+        <v>499</v>
+      </c>
+      <c r="F28" t="s">
+        <v>439</v>
+      </c>
+      <c r="G28" t="s">
+        <v>440</v>
+      </c>
+      <c r="H28" t="s">
+        <v>436</v>
+      </c>
+      <c r="I28" t="s">
+        <v>436</v>
+      </c>
+      <c r="J28" t="s">
+        <v>441</v>
+      </c>
+      <c r="K28" t="s">
+        <v>436</v>
+      </c>
+      <c r="L28" t="s">
+        <v>436</v>
+      </c>
+      <c r="M28" t="s">
+        <v>442</v>
+      </c>
+      <c r="N28" t="s">
+        <v>443</v>
+      </c>
+      <c r="O28" t="s">
+        <v>451</v>
+      </c>
+      <c r="P28" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17">
+      <c r="B29" t="s">
+        <v>731</v>
+      </c>
+      <c r="C29" t="s">
+        <v>436</v>
+      </c>
+      <c r="D29" t="s">
+        <v>502</v>
+      </c>
+      <c r="E29" t="s">
+        <v>503</v>
+      </c>
+      <c r="F29" t="s">
+        <v>439</v>
+      </c>
+      <c r="G29" t="s">
+        <v>440</v>
+      </c>
+      <c r="H29" t="s">
+        <v>436</v>
+      </c>
+      <c r="I29" t="s">
+        <v>436</v>
+      </c>
+      <c r="J29" t="s">
+        <v>441</v>
+      </c>
+      <c r="K29" t="s">
+        <v>436</v>
+      </c>
+      <c r="L29" t="s">
+        <v>436</v>
+      </c>
+      <c r="M29" t="s">
+        <v>442</v>
+      </c>
+      <c r="N29" t="s">
+        <v>443</v>
+      </c>
+      <c r="O29" t="s">
+        <v>451</v>
+      </c>
+      <c r="P29" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17">
+      <c r="B30" t="s">
+        <v>729</v>
+      </c>
+      <c r="C30" t="s">
+        <v>436</v>
+      </c>
+      <c r="D30" t="s">
+        <v>485</v>
+      </c>
+      <c r="E30" t="s">
+        <v>486</v>
+      </c>
+      <c r="F30" t="s">
+        <v>439</v>
+      </c>
+      <c r="G30" t="s">
+        <v>440</v>
+      </c>
+      <c r="H30" t="s">
+        <v>436</v>
+      </c>
+      <c r="I30" t="s">
+        <v>436</v>
+      </c>
+      <c r="J30" t="s">
+        <v>441</v>
+      </c>
+      <c r="K30" t="s">
+        <v>436</v>
+      </c>
+      <c r="L30" t="s">
+        <v>436</v>
+      </c>
+      <c r="M30" t="s">
+        <v>442</v>
+      </c>
+      <c r="N30" t="s">
+        <v>443</v>
+      </c>
+      <c r="O30" t="s">
+        <v>451</v>
+      </c>
+      <c r="P30" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17">
+      <c r="B31" t="s">
+        <v>732</v>
+      </c>
+      <c r="C31" t="s">
+        <v>436</v>
+      </c>
+      <c r="D31" t="s">
+        <v>506</v>
+      </c>
+      <c r="E31" t="s">
+        <v>507</v>
+      </c>
+      <c r="F31" t="s">
+        <v>439</v>
+      </c>
+      <c r="G31" t="s">
+        <v>440</v>
+      </c>
+      <c r="H31" t="s">
+        <v>436</v>
+      </c>
+      <c r="I31" t="s">
+        <v>436</v>
+      </c>
+      <c r="J31" t="s">
+        <v>441</v>
+      </c>
+      <c r="K31" t="s">
+        <v>436</v>
+      </c>
+      <c r="L31" t="s">
+        <v>436</v>
+      </c>
+      <c r="M31" t="s">
+        <v>442</v>
+      </c>
+      <c r="N31" t="s">
+        <v>443</v>
+      </c>
+      <c r="O31" t="s">
+        <v>451</v>
+      </c>
+      <c r="P31" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17">
+      <c r="B32" t="s">
+        <v>733</v>
+      </c>
+      <c r="C32" t="s">
+        <v>436</v>
+      </c>
+      <c r="D32" t="s">
+        <v>510</v>
+      </c>
+      <c r="E32" t="s">
+        <v>511</v>
+      </c>
+      <c r="F32" t="s">
+        <v>439</v>
+      </c>
+      <c r="G32" t="s">
+        <v>440</v>
+      </c>
+      <c r="H32" t="s">
+        <v>436</v>
+      </c>
+      <c r="I32" t="s">
+        <v>436</v>
+      </c>
+      <c r="J32" t="s">
+        <v>441</v>
+      </c>
+      <c r="K32" t="s">
+        <v>436</v>
+      </c>
+      <c r="L32" t="s">
+        <v>436</v>
+      </c>
+      <c r="M32" t="s">
+        <v>442</v>
+      </c>
+      <c r="N32" t="s">
+        <v>443</v>
+      </c>
+      <c r="O32" t="s">
+        <v>451</v>
+      </c>
+      <c r="P32" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17">
+      <c r="B33" t="s">
+        <v>488</v>
+      </c>
+      <c r="C33" t="s">
+        <v>436</v>
+      </c>
+      <c r="D33" t="s">
+        <v>489</v>
+      </c>
+      <c r="E33" t="s">
+        <v>490</v>
+      </c>
+      <c r="F33" t="s">
+        <v>439</v>
+      </c>
+      <c r="G33" t="s">
+        <v>440</v>
+      </c>
+      <c r="H33" t="s">
+        <v>436</v>
+      </c>
+      <c r="I33" t="s">
+        <v>436</v>
+      </c>
+      <c r="J33" t="s">
+        <v>491</v>
+      </c>
+      <c r="K33" t="s">
+        <v>436</v>
+      </c>
+      <c r="L33" t="s">
+        <v>436</v>
+      </c>
+      <c r="M33" t="s">
+        <v>442</v>
+      </c>
+      <c r="N33" t="s">
+        <v>443</v>
+      </c>
+      <c r="O33" t="s">
+        <v>465</v>
+      </c>
+      <c r="P33" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17">
+      <c r="B34" t="s">
+        <v>493</v>
+      </c>
+      <c r="C34" t="s">
+        <v>436</v>
+      </c>
+      <c r="D34" t="s">
+        <v>494</v>
+      </c>
+      <c r="E34" t="s">
+        <v>495</v>
+      </c>
+      <c r="F34" t="s">
+        <v>439</v>
+      </c>
+      <c r="G34" t="s">
+        <v>440</v>
+      </c>
+      <c r="H34" t="s">
+        <v>436</v>
+      </c>
+      <c r="I34" t="s">
+        <v>436</v>
+      </c>
+      <c r="J34" t="s">
+        <v>491</v>
+      </c>
+      <c r="K34" t="s">
+        <v>436</v>
+      </c>
+      <c r="L34" t="s">
+        <v>436</v>
+      </c>
+      <c r="M34" t="s">
+        <v>442</v>
+      </c>
+      <c r="N34" t="s">
+        <v>443</v>
+      </c>
+      <c r="O34" t="s">
+        <v>465</v>
+      </c>
+      <c r="P34" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17">
+      <c r="B35" t="s">
+        <v>930</v>
+      </c>
+      <c r="C35" t="s">
+        <v>436</v>
+      </c>
+      <c r="D35" t="s">
+        <v>931</v>
+      </c>
+      <c r="E35" t="s">
+        <v>932</v>
+      </c>
+      <c r="F35" t="s">
+        <v>439</v>
+      </c>
+      <c r="G35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H35" t="s">
+        <v>436</v>
+      </c>
+      <c r="I35" t="s">
+        <v>436</v>
+      </c>
+      <c r="J35" t="s">
+        <v>441</v>
+      </c>
+      <c r="K35" t="s">
+        <v>436</v>
+      </c>
+      <c r="L35" t="s">
+        <v>436</v>
+      </c>
+      <c r="M35" t="s">
+        <v>440</v>
+      </c>
+      <c r="N35" t="s">
+        <v>443</v>
+      </c>
+      <c r="O35" t="s">
+        <v>444</v>
+      </c>
+      <c r="P35" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="36" spans="2:17">
+      <c r="B36" t="s">
+        <v>934</v>
+      </c>
+      <c r="C36" t="s">
+        <v>436</v>
+      </c>
+      <c r="D36" t="s">
+        <v>935</v>
+      </c>
+      <c r="E36" t="s">
+        <v>936</v>
+      </c>
+      <c r="F36" t="s">
+        <v>439</v>
+      </c>
+      <c r="G36" t="s">
+        <v>440</v>
+      </c>
+      <c r="H36" t="s">
+        <v>436</v>
+      </c>
+      <c r="I36" t="s">
+        <v>436</v>
+      </c>
+      <c r="J36" t="s">
+        <v>441</v>
+      </c>
+      <c r="K36" t="s">
+        <v>436</v>
+      </c>
+      <c r="L36" t="s">
+        <v>436</v>
+      </c>
+      <c r="M36" t="s">
+        <v>440</v>
+      </c>
+      <c r="N36" t="s">
+        <v>443</v>
+      </c>
+      <c r="O36" t="s">
+        <v>444</v>
+      </c>
+      <c r="P36" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="38" spans="2:17">
+      <c r="B38" t="s">
+        <v>938</v>
+      </c>
+      <c r="C38" t="s">
+        <v>436</v>
+      </c>
+      <c r="D38" t="s">
+        <v>939</v>
+      </c>
+      <c r="E38" t="s">
+        <v>940</v>
+      </c>
+      <c r="F38" t="s">
+        <v>439</v>
+      </c>
+      <c r="G38" t="s">
+        <v>442</v>
+      </c>
+      <c r="H38" t="s">
+        <v>436</v>
+      </c>
+      <c r="I38" t="s">
+        <v>941</v>
+      </c>
+      <c r="J38" t="s">
+        <v>491</v>
+      </c>
+      <c r="K38" t="s">
+        <v>436</v>
+      </c>
+      <c r="L38" t="s">
+        <v>436</v>
+      </c>
+      <c r="M38" t="s">
+        <v>442</v>
+      </c>
+      <c r="N38" t="s">
+        <v>443</v>
+      </c>
+      <c r="O38" t="s">
+        <v>465</v>
+      </c>
+      <c r="P38" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17">
+      <c r="B39" t="s">
+        <v>943</v>
+      </c>
+      <c r="C39" t="s">
+        <v>436</v>
+      </c>
+      <c r="D39" t="s">
+        <v>944</v>
+      </c>
+      <c r="E39" t="s">
+        <v>945</v>
+      </c>
+      <c r="F39" t="s">
+        <v>439</v>
+      </c>
+      <c r="G39" t="s">
+        <v>440</v>
+      </c>
+      <c r="H39" t="s">
+        <v>436</v>
+      </c>
+      <c r="I39" t="s">
+        <v>436</v>
+      </c>
+      <c r="J39" t="s">
+        <v>441</v>
+      </c>
+      <c r="K39" t="s">
+        <v>436</v>
+      </c>
+      <c r="L39" t="s">
+        <v>436</v>
+      </c>
+      <c r="M39" t="s">
+        <v>442</v>
+      </c>
+      <c r="N39" t="s">
+        <v>443</v>
+      </c>
+      <c r="O39" t="s">
+        <v>562</v>
+      </c>
+      <c r="P39" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="40" spans="2:17">
+      <c r="B40" t="s">
+        <v>947</v>
+      </c>
+      <c r="C40" t="s">
+        <v>436</v>
+      </c>
+      <c r="D40" t="s">
+        <v>948</v>
+      </c>
+      <c r="E40" t="s">
+        <v>949</v>
+      </c>
+      <c r="F40" t="s">
+        <v>439</v>
+      </c>
+      <c r="G40" t="s">
+        <v>440</v>
+      </c>
+      <c r="H40" t="s">
+        <v>436</v>
+      </c>
+      <c r="I40" t="s">
+        <v>436</v>
+      </c>
+      <c r="J40" t="s">
+        <v>516</v>
+      </c>
+      <c r="K40" t="s">
+        <v>450</v>
+      </c>
+      <c r="L40" t="s">
+        <v>436</v>
+      </c>
+      <c r="M40" t="s">
+        <v>442</v>
+      </c>
+      <c r="N40" t="s">
+        <v>443</v>
+      </c>
+      <c r="O40" t="s">
+        <v>456</v>
+      </c>
+      <c r="P40" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="41" spans="2:17">
+      <c r="B41" t="s">
+        <v>513</v>
+      </c>
+      <c r="C41" t="s">
+        <v>436</v>
+      </c>
+      <c r="D41" t="s">
+        <v>514</v>
+      </c>
+      <c r="E41" t="s">
+        <v>515</v>
+      </c>
+      <c r="F41" t="s">
+        <v>439</v>
+      </c>
+      <c r="G41" t="s">
+        <v>440</v>
+      </c>
+      <c r="H41" t="s">
+        <v>436</v>
+      </c>
+      <c r="I41" t="s">
+        <v>436</v>
+      </c>
+      <c r="J41" t="s">
+        <v>516</v>
+      </c>
+      <c r="K41" t="s">
+        <v>450</v>
+      </c>
+      <c r="L41" t="s">
+        <v>436</v>
+      </c>
+      <c r="M41" t="s">
+        <v>442</v>
+      </c>
+      <c r="N41" t="s">
+        <v>443</v>
+      </c>
+      <c r="O41" t="s">
+        <v>456</v>
+      </c>
+      <c r="P41" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17">
+      <c r="B42" t="s">
+        <v>951</v>
+      </c>
+      <c r="C42" t="s">
+        <v>436</v>
+      </c>
+      <c r="D42" t="s">
+        <v>952</v>
+      </c>
+      <c r="E42" t="s">
+        <v>953</v>
+      </c>
+      <c r="F42" t="s">
+        <v>439</v>
+      </c>
+      <c r="G42" t="s">
+        <v>440</v>
+      </c>
+      <c r="H42" t="s">
+        <v>436</v>
+      </c>
+      <c r="I42" t="s">
+        <v>436</v>
+      </c>
+      <c r="J42" t="s">
+        <v>441</v>
+      </c>
+      <c r="K42" t="s">
+        <v>436</v>
+      </c>
+      <c r="L42" t="s">
+        <v>436</v>
+      </c>
+      <c r="M42" t="s">
+        <v>440</v>
+      </c>
+      <c r="N42" t="s">
+        <v>443</v>
+      </c>
+      <c r="O42" t="s">
+        <v>444</v>
+      </c>
+      <c r="P42" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17">
+      <c r="B43" t="s">
+        <v>955</v>
+      </c>
+      <c r="C43" t="s">
+        <v>436</v>
+      </c>
+      <c r="D43" t="s">
+        <v>956</v>
+      </c>
+      <c r="E43" t="s">
+        <v>957</v>
+      </c>
+      <c r="F43" t="s">
+        <v>439</v>
+      </c>
+      <c r="G43" t="s">
+        <v>440</v>
+      </c>
+      <c r="H43" t="s">
+        <v>436</v>
+      </c>
+      <c r="I43" t="s">
+        <v>436</v>
+      </c>
+      <c r="J43" t="s">
+        <v>441</v>
+      </c>
+      <c r="K43" t="s">
+        <v>436</v>
+      </c>
+      <c r="L43" t="s">
+        <v>436</v>
+      </c>
+      <c r="M43" t="s">
+        <v>440</v>
+      </c>
+      <c r="N43" t="s">
+        <v>443</v>
+      </c>
+      <c r="O43" t="s">
+        <v>444</v>
+      </c>
+      <c r="P43" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17">
+      <c r="B45" t="s">
+        <v>447</v>
+      </c>
+      <c r="C45" t="s">
+        <v>436</v>
+      </c>
+      <c r="D45" t="s">
+        <v>448</v>
+      </c>
+      <c r="E45" t="s">
+        <v>449</v>
+      </c>
+      <c r="F45" t="s">
+        <v>439</v>
+      </c>
+      <c r="G45" t="s">
+        <v>440</v>
+      </c>
+      <c r="H45" t="s">
+        <v>436</v>
+      </c>
+      <c r="I45" t="s">
+        <v>436</v>
+      </c>
+      <c r="J45" t="s">
+        <v>441</v>
+      </c>
+      <c r="K45" t="s">
+        <v>450</v>
+      </c>
+      <c r="L45" t="s">
+        <v>436</v>
+      </c>
+      <c r="M45" t="s">
+        <v>442</v>
+      </c>
+      <c r="N45" t="s">
+        <v>443</v>
+      </c>
+      <c r="O45" t="s">
+        <v>451</v>
+      </c>
+      <c r="P45" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17">
+      <c r="B46" t="s">
+        <v>959</v>
+      </c>
+      <c r="C46" t="s">
+        <v>436</v>
+      </c>
+      <c r="D46" t="s">
+        <v>960</v>
+      </c>
+      <c r="E46" t="s">
+        <v>961</v>
+      </c>
+      <c r="F46" t="s">
+        <v>439</v>
+      </c>
+      <c r="G46" t="s">
+        <v>440</v>
+      </c>
+      <c r="H46" t="s">
+        <v>797</v>
+      </c>
+      <c r="I46" t="s">
+        <v>798</v>
+      </c>
+      <c r="J46" t="s">
+        <v>516</v>
+      </c>
+      <c r="K46" t="s">
+        <v>450</v>
+      </c>
+      <c r="L46" t="s">
+        <v>436</v>
+      </c>
+      <c r="M46" t="s">
+        <v>442</v>
+      </c>
+      <c r="N46" t="s">
+        <v>443</v>
+      </c>
+      <c r="O46" t="s">
+        <v>451</v>
+      </c>
+      <c r="P46" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17">
+      <c r="B47" t="s">
+        <v>453</v>
+      </c>
+      <c r="C47" t="s">
+        <v>436</v>
+      </c>
+      <c r="D47" t="s">
+        <v>454</v>
+      </c>
+      <c r="E47" t="s">
+        <v>455</v>
+      </c>
+      <c r="F47" t="s">
+        <v>439</v>
+      </c>
+      <c r="G47" t="s">
+        <v>440</v>
+      </c>
+      <c r="H47" t="s">
+        <v>436</v>
+      </c>
+      <c r="I47" t="s">
+        <v>436</v>
+      </c>
+      <c r="J47" t="s">
+        <v>441</v>
+      </c>
+      <c r="K47" t="s">
+        <v>450</v>
+      </c>
+      <c r="L47" t="s">
+        <v>436</v>
+      </c>
+      <c r="M47" t="s">
+        <v>442</v>
+      </c>
+      <c r="N47" t="s">
+        <v>443</v>
+      </c>
+      <c r="O47" t="s">
+        <v>456</v>
+      </c>
+      <c r="P47" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17">
+      <c r="B48" t="s">
+        <v>635</v>
+      </c>
+      <c r="C48" t="s">
+        <v>436</v>
+      </c>
+      <c r="D48" t="s">
+        <v>636</v>
+      </c>
+      <c r="E48" t="s">
+        <v>637</v>
+      </c>
+      <c r="F48" t="s">
+        <v>439</v>
+      </c>
+      <c r="G48" t="s">
+        <v>440</v>
+      </c>
+      <c r="H48" t="s">
+        <v>436</v>
+      </c>
+      <c r="I48" t="s">
+        <v>436</v>
+      </c>
+      <c r="J48" t="s">
+        <v>441</v>
+      </c>
+      <c r="K48" t="s">
+        <v>450</v>
+      </c>
+      <c r="L48" t="s">
+        <v>436</v>
+      </c>
+      <c r="M48" t="s">
+        <v>442</v>
+      </c>
+      <c r="N48" t="s">
+        <v>443</v>
+      </c>
+      <c r="O48" t="s">
+        <v>562</v>
+      </c>
+      <c r="P48" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="49" spans="2:17">
+      <c r="B49" t="s">
+        <v>751</v>
+      </c>
+      <c r="C49" t="s">
+        <v>436</v>
+      </c>
+      <c r="D49" t="s">
+        <v>752</v>
+      </c>
+      <c r="E49" t="s">
+        <v>753</v>
+      </c>
+      <c r="F49" t="s">
+        <v>439</v>
+      </c>
+      <c r="G49" t="s">
+        <v>440</v>
+      </c>
+      <c r="H49" t="s">
+        <v>436</v>
+      </c>
+      <c r="I49" t="s">
+        <v>436</v>
+      </c>
+      <c r="J49" t="s">
+        <v>441</v>
+      </c>
+      <c r="K49" t="s">
+        <v>450</v>
+      </c>
+      <c r="L49" t="s">
+        <v>436</v>
+      </c>
+      <c r="M49" t="s">
+        <v>442</v>
+      </c>
+      <c r="N49" t="s">
+        <v>443</v>
+      </c>
+      <c r="O49" t="s">
+        <v>562</v>
+      </c>
+      <c r="P49" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="50" spans="2:17">
+      <c r="B50" t="s">
+        <v>639</v>
+      </c>
+      <c r="C50" t="s">
+        <v>436</v>
+      </c>
+      <c r="D50" t="s">
+        <v>640</v>
+      </c>
+      <c r="E50" t="s">
+        <v>641</v>
+      </c>
+      <c r="F50" t="s">
+        <v>439</v>
+      </c>
+      <c r="G50" t="s">
+        <v>440</v>
+      </c>
+      <c r="H50" t="s">
+        <v>436</v>
+      </c>
+      <c r="I50" t="s">
+        <v>436</v>
+      </c>
+      <c r="J50" t="s">
+        <v>441</v>
+      </c>
+      <c r="K50" t="s">
+        <v>436</v>
+      </c>
+      <c r="L50" t="s">
+        <v>436</v>
+      </c>
+      <c r="M50" t="s">
+        <v>442</v>
+      </c>
+      <c r="N50" t="s">
+        <v>443</v>
+      </c>
+      <c r="O50" t="s">
+        <v>450</v>
+      </c>
+      <c r="P50" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="51" spans="2:17">
+      <c r="B51" t="s">
+        <v>963</v>
+      </c>
+      <c r="C51" t="s">
+        <v>436</v>
+      </c>
+      <c r="D51" t="s">
+        <v>964</v>
+      </c>
+      <c r="E51" t="s">
+        <v>965</v>
+      </c>
+      <c r="F51" t="s">
+        <v>439</v>
+      </c>
+      <c r="G51" t="s">
+        <v>440</v>
+      </c>
+      <c r="H51" t="s">
+        <v>436</v>
+      </c>
+      <c r="I51" t="s">
+        <v>436</v>
+      </c>
+      <c r="J51" t="s">
+        <v>441</v>
+      </c>
+      <c r="K51" t="s">
+        <v>436</v>
+      </c>
+      <c r="L51" t="s">
+        <v>436</v>
+      </c>
+      <c r="M51" t="s">
+        <v>440</v>
+      </c>
+      <c r="N51" t="s">
+        <v>443</v>
+      </c>
+      <c r="O51" t="s">
+        <v>444</v>
+      </c>
+      <c r="P51" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="52" spans="2:17">
+      <c r="B52" t="s">
+        <v>967</v>
+      </c>
+      <c r="C52" t="s">
+        <v>436</v>
+      </c>
+      <c r="D52" t="s">
+        <v>968</v>
+      </c>
+      <c r="E52" t="s">
+        <v>969</v>
+      </c>
+      <c r="F52" t="s">
+        <v>439</v>
+      </c>
+      <c r="G52" t="s">
+        <v>440</v>
+      </c>
+      <c r="H52" t="s">
+        <v>436</v>
+      </c>
+      <c r="I52" t="s">
+        <v>436</v>
+      </c>
+      <c r="J52" t="s">
+        <v>441</v>
+      </c>
+      <c r="K52" t="s">
+        <v>436</v>
+      </c>
+      <c r="L52" t="s">
+        <v>436</v>
+      </c>
+      <c r="M52" t="s">
+        <v>440</v>
+      </c>
+      <c r="N52" t="s">
+        <v>443</v>
+      </c>
+      <c r="O52" t="s">
+        <v>444</v>
+      </c>
+      <c r="P52" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="54" spans="2:17">
+      <c r="B54" t="s">
+        <v>971</v>
+      </c>
+      <c r="C54" t="s">
+        <v>436</v>
+      </c>
+      <c r="D54" t="s">
+        <v>972</v>
+      </c>
+      <c r="E54" t="s">
+        <v>973</v>
+      </c>
+      <c r="F54" t="s">
+        <v>439</v>
+      </c>
+      <c r="G54" t="s">
+        <v>440</v>
+      </c>
+      <c r="H54" t="s">
+        <v>436</v>
+      </c>
+      <c r="I54" t="s">
+        <v>436</v>
+      </c>
+      <c r="J54" t="s">
+        <v>441</v>
+      </c>
+      <c r="K54" t="s">
+        <v>450</v>
+      </c>
+      <c r="L54" t="s">
+        <v>436</v>
+      </c>
+      <c r="M54" t="s">
+        <v>442</v>
+      </c>
+      <c r="N54" t="s">
+        <v>443</v>
+      </c>
+      <c r="O54" t="s">
+        <v>451</v>
+      </c>
+      <c r="P54" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="55" spans="2:17">
+      <c r="B55" t="s">
+        <v>975</v>
+      </c>
+      <c r="C55" t="s">
+        <v>436</v>
+      </c>
+      <c r="D55" t="s">
+        <v>976</v>
+      </c>
+      <c r="E55" t="s">
+        <v>977</v>
+      </c>
+      <c r="F55" t="s">
+        <v>439</v>
+      </c>
+      <c r="G55" t="s">
+        <v>440</v>
+      </c>
+      <c r="H55" t="s">
+        <v>797</v>
+      </c>
+      <c r="I55" t="s">
+        <v>798</v>
+      </c>
+      <c r="J55" t="s">
+        <v>516</v>
+      </c>
+      <c r="K55" t="s">
+        <v>450</v>
+      </c>
+      <c r="L55" t="s">
+        <v>436</v>
+      </c>
+      <c r="M55" t="s">
+        <v>442</v>
+      </c>
+      <c r="N55" t="s">
+        <v>443</v>
+      </c>
+      <c r="O55" t="s">
+        <v>451</v>
+      </c>
+      <c r="P55" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="56" spans="2:17">
+      <c r="B56" t="s">
+        <v>458</v>
+      </c>
+      <c r="C56" t="s">
+        <v>436</v>
+      </c>
+      <c r="D56" t="s">
+        <v>459</v>
+      </c>
+      <c r="E56" t="s">
+        <v>460</v>
+      </c>
+      <c r="F56" t="s">
+        <v>439</v>
+      </c>
+      <c r="G56" t="s">
+        <v>440</v>
+      </c>
+      <c r="H56" t="s">
+        <v>436</v>
+      </c>
+      <c r="I56" t="s">
+        <v>436</v>
+      </c>
+      <c r="J56" t="s">
+        <v>441</v>
+      </c>
+      <c r="K56" t="s">
+        <v>450</v>
+      </c>
+      <c r="L56" t="s">
+        <v>436</v>
+      </c>
+      <c r="M56" t="s">
+        <v>442</v>
+      </c>
+      <c r="N56" t="s">
+        <v>443</v>
+      </c>
+      <c r="O56" t="s">
+        <v>456</v>
+      </c>
+      <c r="P56" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="57" spans="2:17">
+      <c r="B57" t="s">
+        <v>979</v>
+      </c>
+      <c r="C57" t="s">
+        <v>436</v>
+      </c>
+      <c r="D57" t="s">
+        <v>980</v>
+      </c>
+      <c r="E57" t="s">
+        <v>981</v>
+      </c>
+      <c r="F57" t="s">
+        <v>439</v>
+      </c>
+      <c r="G57" t="s">
+        <v>440</v>
+      </c>
+      <c r="H57" t="s">
+        <v>436</v>
+      </c>
+      <c r="I57" t="s">
+        <v>436</v>
+      </c>
+      <c r="J57" t="s">
+        <v>441</v>
+      </c>
+      <c r="K57" t="s">
+        <v>465</v>
+      </c>
+      <c r="L57" t="s">
+        <v>436</v>
+      </c>
+      <c r="M57" t="s">
+        <v>442</v>
+      </c>
+      <c r="N57" t="s">
+        <v>443</v>
+      </c>
+      <c r="O57" t="s">
+        <v>456</v>
+      </c>
+      <c r="P57" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="58" spans="2:17">
+      <c r="B58" t="s">
+        <v>983</v>
+      </c>
+      <c r="C58" t="s">
+        <v>436</v>
+      </c>
+      <c r="D58" t="s">
+        <v>984</v>
+      </c>
+      <c r="E58" t="s">
+        <v>985</v>
+      </c>
+      <c r="F58" t="s">
+        <v>439</v>
+      </c>
+      <c r="G58" t="s">
+        <v>440</v>
+      </c>
+      <c r="H58" t="s">
+        <v>436</v>
+      </c>
+      <c r="I58" t="s">
+        <v>436</v>
+      </c>
+      <c r="J58" t="s">
+        <v>441</v>
+      </c>
+      <c r="K58" t="s">
+        <v>465</v>
+      </c>
+      <c r="L58" t="s">
+        <v>436</v>
+      </c>
+      <c r="M58" t="s">
+        <v>442</v>
+      </c>
+      <c r="N58" t="s">
+        <v>443</v>
+      </c>
+      <c r="O58" t="s">
+        <v>456</v>
+      </c>
+      <c r="P58" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="59" spans="2:17">
+      <c r="B59" t="s">
+        <v>613</v>
+      </c>
+      <c r="C59" t="s">
+        <v>436</v>
+      </c>
+      <c r="D59" t="s">
+        <v>614</v>
+      </c>
+      <c r="E59" t="s">
+        <v>615</v>
+      </c>
+      <c r="F59" t="s">
+        <v>439</v>
+      </c>
+      <c r="G59" t="s">
+        <v>440</v>
+      </c>
+      <c r="H59" t="s">
+        <v>436</v>
+      </c>
+      <c r="I59" t="s">
+        <v>436</v>
+      </c>
+      <c r="J59" t="s">
+        <v>516</v>
+      </c>
+      <c r="K59" t="s">
+        <v>450</v>
+      </c>
+      <c r="L59" t="s">
+        <v>436</v>
+      </c>
+      <c r="M59" t="s">
+        <v>442</v>
+      </c>
+      <c r="N59" t="s">
+        <v>443</v>
+      </c>
+      <c r="O59" t="s">
+        <v>555</v>
+      </c>
+      <c r="P59" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="60" spans="2:17">
+      <c r="B60" t="s">
+        <v>987</v>
+      </c>
+      <c r="C60" t="s">
+        <v>436</v>
+      </c>
+      <c r="D60" t="s">
+        <v>988</v>
+      </c>
+      <c r="E60" t="s">
+        <v>989</v>
+      </c>
+      <c r="F60" t="s">
+        <v>439</v>
+      </c>
+      <c r="G60" t="s">
+        <v>440</v>
+      </c>
+      <c r="H60" t="s">
+        <v>436</v>
+      </c>
+      <c r="I60" t="s">
+        <v>436</v>
+      </c>
+      <c r="J60" t="s">
+        <v>441</v>
+      </c>
+      <c r="K60" t="s">
+        <v>436</v>
+      </c>
+      <c r="L60" t="s">
+        <v>436</v>
+      </c>
+      <c r="M60" t="s">
+        <v>440</v>
+      </c>
+      <c r="N60" t="s">
+        <v>443</v>
+      </c>
+      <c r="O60" t="s">
+        <v>444</v>
+      </c>
+      <c r="P60" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="61" spans="2:17">
+      <c r="B61" t="s">
+        <v>991</v>
+      </c>
+      <c r="C61" t="s">
+        <v>436</v>
+      </c>
+      <c r="D61" t="s">
+        <v>992</v>
+      </c>
+      <c r="E61" t="s">
+        <v>993</v>
+      </c>
+      <c r="F61" t="s">
+        <v>439</v>
+      </c>
+      <c r="G61" t="s">
+        <v>440</v>
+      </c>
+      <c r="H61" t="s">
+        <v>436</v>
+      </c>
+      <c r="I61" t="s">
+        <v>436</v>
+      </c>
+      <c r="J61" t="s">
+        <v>441</v>
+      </c>
+      <c r="K61" t="s">
+        <v>436</v>
+      </c>
+      <c r="L61" t="s">
+        <v>436</v>
+      </c>
+      <c r="M61" t="s">
+        <v>440</v>
+      </c>
+      <c r="N61" t="s">
+        <v>443</v>
+      </c>
+      <c r="O61" t="s">
+        <v>444</v>
+      </c>
+      <c r="P61" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="63" spans="2:17">
+      <c r="B63" t="s">
+        <v>995</v>
+      </c>
+      <c r="C63" t="s">
+        <v>436</v>
+      </c>
+      <c r="D63" t="s">
+        <v>996</v>
+      </c>
+      <c r="E63" t="s">
+        <v>997</v>
+      </c>
+      <c r="F63" t="s">
+        <v>439</v>
+      </c>
+      <c r="G63" t="s">
+        <v>442</v>
+      </c>
+      <c r="H63" t="s">
+        <v>436</v>
+      </c>
+      <c r="I63" t="s">
+        <v>465</v>
+      </c>
+      <c r="J63" t="s">
+        <v>441</v>
+      </c>
+      <c r="K63" t="s">
+        <v>436</v>
+      </c>
+      <c r="L63" t="s">
+        <v>436</v>
+      </c>
+      <c r="M63" t="s">
+        <v>442</v>
+      </c>
+      <c r="N63" t="s">
+        <v>443</v>
+      </c>
+      <c r="O63" t="s">
+        <v>450</v>
+      </c>
+      <c r="P63" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="64" spans="2:17">
+      <c r="B64" t="s">
+        <v>999</v>
+      </c>
+      <c r="C64" t="s">
+        <v>436</v>
+      </c>
+      <c r="D64" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E64" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F64" t="s">
+        <v>439</v>
+      </c>
+      <c r="G64" t="s">
+        <v>440</v>
+      </c>
+      <c r="H64" t="s">
+        <v>436</v>
+      </c>
+      <c r="I64" t="s">
+        <v>436</v>
+      </c>
+      <c r="J64" t="s">
+        <v>441</v>
+      </c>
+      <c r="K64" t="s">
+        <v>436</v>
+      </c>
+      <c r="L64" t="s">
+        <v>436</v>
+      </c>
+      <c r="M64" t="s">
+        <v>442</v>
+      </c>
+      <c r="N64" t="s">
+        <v>443</v>
+      </c>
+      <c r="O64" t="s">
+        <v>555</v>
+      </c>
+      <c r="P64" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17">
+      <c r="B65" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C65" t="s">
+        <v>436</v>
+      </c>
+      <c r="D65" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E65" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F65" t="s">
+        <v>439</v>
+      </c>
+      <c r="G65" t="s">
+        <v>440</v>
+      </c>
+      <c r="H65" t="s">
+        <v>436</v>
+      </c>
+      <c r="I65" t="s">
+        <v>436</v>
+      </c>
+      <c r="J65" t="s">
+        <v>441</v>
+      </c>
+      <c r="K65" t="s">
+        <v>436</v>
+      </c>
+      <c r="L65" t="s">
+        <v>436</v>
+      </c>
+      <c r="M65" t="s">
+        <v>442</v>
+      </c>
+      <c r="N65" t="s">
+        <v>443</v>
+      </c>
+      <c r="O65" t="s">
+        <v>555</v>
+      </c>
+      <c r="P65" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17">
+      <c r="B66" t="s">
+        <v>618</v>
+      </c>
+      <c r="C66" t="s">
+        <v>436</v>
+      </c>
+      <c r="D66" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E66" t="s">
+        <v>1008</v>
+      </c>
+      <c r="F66" t="s">
+        <v>439</v>
+      </c>
+      <c r="G66" t="s">
+        <v>442</v>
+      </c>
+      <c r="H66" t="s">
+        <v>436</v>
+      </c>
+      <c r="I66" t="s">
+        <v>450</v>
+      </c>
+      <c r="J66" t="s">
+        <v>441</v>
+      </c>
+      <c r="K66" t="s">
+        <v>436</v>
+      </c>
+      <c r="L66" t="s">
+        <v>436</v>
+      </c>
+      <c r="M66" t="s">
+        <v>442</v>
+      </c>
+      <c r="N66" t="s">
+        <v>443</v>
+      </c>
+      <c r="O66" t="s">
+        <v>450</v>
+      </c>
+      <c r="P66" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17">
+      <c r="B67" t="s">
+        <v>622</v>
+      </c>
+      <c r="C67" t="s">
+        <v>436</v>
+      </c>
+      <c r="D67" t="s">
+        <v>1009</v>
+      </c>
+      <c r="E67" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F67" t="s">
+        <v>439</v>
+      </c>
+      <c r="G67" t="s">
+        <v>440</v>
+      </c>
+      <c r="H67" t="s">
+        <v>436</v>
+      </c>
+      <c r="I67" t="s">
+        <v>436</v>
+      </c>
+      <c r="J67" t="s">
+        <v>441</v>
+      </c>
+      <c r="K67" t="s">
+        <v>450</v>
+      </c>
+      <c r="L67" t="s">
+        <v>436</v>
+      </c>
+      <c r="M67" t="s">
+        <v>442</v>
+      </c>
+      <c r="N67" t="s">
+        <v>443</v>
+      </c>
+      <c r="O67" t="s">
+        <v>562</v>
+      </c>
+      <c r="P67" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="68" spans="2:17">
+      <c r="B68" t="s">
+        <v>626</v>
+      </c>
+      <c r="C68" t="s">
+        <v>436</v>
+      </c>
+      <c r="D68" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E68" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F68" t="s">
+        <v>439</v>
+      </c>
+      <c r="G68" t="s">
+        <v>440</v>
+      </c>
+      <c r="H68" t="s">
+        <v>436</v>
+      </c>
+      <c r="I68" t="s">
+        <v>436</v>
+      </c>
+      <c r="J68" t="s">
+        <v>441</v>
+      </c>
+      <c r="K68" t="s">
+        <v>450</v>
+      </c>
+      <c r="L68" t="s">
+        <v>436</v>
+      </c>
+      <c r="M68" t="s">
+        <v>440</v>
+      </c>
+      <c r="N68" t="s">
+        <v>443</v>
+      </c>
+      <c r="O68" t="s">
+        <v>451</v>
+      </c>
+      <c r="P68" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17">
+      <c r="B69" t="s">
+        <v>630</v>
+      </c>
+      <c r="C69" t="s">
+        <v>436</v>
+      </c>
+      <c r="D69" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E69" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F69" t="s">
+        <v>439</v>
+      </c>
+      <c r="G69" t="s">
+        <v>440</v>
+      </c>
+      <c r="H69" t="s">
+        <v>436</v>
+      </c>
+      <c r="I69" t="s">
+        <v>436</v>
+      </c>
+      <c r="J69" t="s">
+        <v>441</v>
+      </c>
+      <c r="K69" t="s">
+        <v>450</v>
+      </c>
+      <c r="L69" t="s">
+        <v>436</v>
+      </c>
+      <c r="M69" t="s">
+        <v>440</v>
+      </c>
+      <c r="N69" t="s">
+        <v>443</v>
+      </c>
+      <c r="O69" t="s">
+        <v>451</v>
+      </c>
+      <c r="P69" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17">
+      <c r="B70" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C70" t="s">
+        <v>436</v>
+      </c>
+      <c r="D70" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E70" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F70" t="s">
+        <v>439</v>
+      </c>
+      <c r="G70" t="s">
+        <v>440</v>
+      </c>
+      <c r="H70" t="s">
+        <v>436</v>
+      </c>
+      <c r="I70" t="s">
+        <v>436</v>
+      </c>
+      <c r="J70" t="s">
+        <v>441</v>
+      </c>
+      <c r="K70" t="s">
+        <v>436</v>
+      </c>
+      <c r="L70" t="s">
+        <v>436</v>
+      </c>
+      <c r="M70" t="s">
+        <v>440</v>
+      </c>
+      <c r="N70" t="s">
+        <v>443</v>
+      </c>
+      <c r="O70" t="s">
+        <v>444</v>
+      </c>
+      <c r="P70" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17">
+      <c r="B71" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C71" t="s">
+        <v>436</v>
+      </c>
+      <c r="D71" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E71" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F71" t="s">
+        <v>439</v>
+      </c>
+      <c r="G71" t="s">
+        <v>440</v>
+      </c>
+      <c r="H71" t="s">
+        <v>436</v>
+      </c>
+      <c r="I71" t="s">
+        <v>436</v>
+      </c>
+      <c r="J71" t="s">
+        <v>441</v>
+      </c>
+      <c r="K71" t="s">
+        <v>436</v>
+      </c>
+      <c r="L71" t="s">
+        <v>436</v>
+      </c>
+      <c r="M71" t="s">
+        <v>440</v>
+      </c>
+      <c r="N71" t="s">
+        <v>443</v>
+      </c>
+      <c r="O71" t="s">
+        <v>444</v>
+      </c>
+      <c r="P71" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17">
+      <c r="B73" t="s">
+        <v>550</v>
+      </c>
+      <c r="C73" t="s">
+        <v>436</v>
+      </c>
+      <c r="D73" t="s">
+        <v>551</v>
+      </c>
+      <c r="E73" t="s">
+        <v>552</v>
+      </c>
+      <c r="F73" t="s">
+        <v>439</v>
+      </c>
+      <c r="G73" t="s">
+        <v>440</v>
+      </c>
+      <c r="H73" t="s">
+        <v>553</v>
+      </c>
+      <c r="I73" t="s">
+        <v>554</v>
+      </c>
+      <c r="J73" t="s">
+        <v>441</v>
+      </c>
+      <c r="K73" t="s">
+        <v>450</v>
+      </c>
+      <c r="L73" t="s">
+        <v>436</v>
+      </c>
+      <c r="M73" t="s">
+        <v>442</v>
+      </c>
+      <c r="N73" t="s">
+        <v>443</v>
+      </c>
+      <c r="O73" t="s">
+        <v>555</v>
+      </c>
+      <c r="P73" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17">
+      <c r="B74" t="s">
+        <v>557</v>
+      </c>
+      <c r="C74" t="s">
+        <v>436</v>
+      </c>
+      <c r="D74" t="s">
+        <v>558</v>
+      </c>
+      <c r="E74" t="s">
+        <v>559</v>
+      </c>
+      <c r="F74" t="s">
+        <v>439</v>
+      </c>
+      <c r="G74" t="s">
+        <v>440</v>
+      </c>
+      <c r="H74" t="s">
+        <v>560</v>
+      </c>
+      <c r="I74" t="s">
+        <v>561</v>
+      </c>
+      <c r="J74" t="s">
+        <v>441</v>
+      </c>
+      <c r="K74" t="s">
+        <v>450</v>
+      </c>
+      <c r="L74" t="s">
+        <v>436</v>
+      </c>
+      <c r="M74" t="s">
+        <v>442</v>
+      </c>
+      <c r="N74" t="s">
+        <v>443</v>
+      </c>
+      <c r="O74" t="s">
+        <v>562</v>
+      </c>
+      <c r="P74" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17">
+      <c r="B75" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C75" t="s">
+        <v>436</v>
+      </c>
+      <c r="D75" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E75" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F75" t="s">
+        <v>439</v>
+      </c>
+      <c r="G75" t="s">
+        <v>440</v>
+      </c>
+      <c r="H75" t="s">
+        <v>436</v>
+      </c>
+      <c r="I75" t="s">
+        <v>436</v>
+      </c>
+      <c r="J75" t="s">
+        <v>441</v>
+      </c>
+      <c r="K75" t="s">
+        <v>436</v>
+      </c>
+      <c r="L75" t="s">
+        <v>436</v>
+      </c>
+      <c r="M75" t="s">
+        <v>440</v>
+      </c>
+      <c r="N75" t="s">
+        <v>443</v>
+      </c>
+      <c r="O75" t="s">
+        <v>444</v>
+      </c>
+      <c r="P75" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17">
+      <c r="B76" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C76" t="s">
+        <v>436</v>
+      </c>
+      <c r="D76" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E76" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F76" t="s">
+        <v>439</v>
+      </c>
+      <c r="G76" t="s">
+        <v>440</v>
+      </c>
+      <c r="H76" t="s">
+        <v>436</v>
+      </c>
+      <c r="I76" t="s">
+        <v>436</v>
+      </c>
+      <c r="J76" t="s">
+        <v>441</v>
+      </c>
+      <c r="K76" t="s">
+        <v>436</v>
+      </c>
+      <c r="L76" t="s">
+        <v>436</v>
+      </c>
+      <c r="M76" t="s">
+        <v>440</v>
+      </c>
+      <c r="N76" t="s">
+        <v>443</v>
+      </c>
+      <c r="O76" t="s">
+        <v>444</v>
+      </c>
+      <c r="P76" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="78" spans="2:17">
+      <c r="B78" t="s">
+        <v>565</v>
+      </c>
+      <c r="C78" t="s">
+        <v>436</v>
+      </c>
+      <c r="D78" t="s">
+        <v>566</v>
+      </c>
+      <c r="E78" t="s">
+        <v>567</v>
+      </c>
+      <c r="F78" t="s">
+        <v>439</v>
+      </c>
+      <c r="G78" t="s">
+        <v>442</v>
+      </c>
+      <c r="H78" t="s">
+        <v>436</v>
+      </c>
+      <c r="I78" t="s">
+        <v>450</v>
+      </c>
+      <c r="J78" t="s">
+        <v>441</v>
+      </c>
+      <c r="K78" t="s">
+        <v>436</v>
+      </c>
+      <c r="L78" t="s">
+        <v>436</v>
+      </c>
+      <c r="M78" t="s">
+        <v>442</v>
+      </c>
+      <c r="N78" t="s">
+        <v>443</v>
+      </c>
+      <c r="O78" t="s">
+        <v>450</v>
+      </c>
+      <c r="P78" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17">
+      <c r="B79" t="s">
+        <v>569</v>
+      </c>
+      <c r="C79" t="s">
+        <v>436</v>
+      </c>
+      <c r="D79" t="s">
+        <v>570</v>
+      </c>
+      <c r="E79" t="s">
+        <v>571</v>
+      </c>
+      <c r="F79" t="s">
+        <v>439</v>
+      </c>
+      <c r="G79" t="s">
+        <v>442</v>
+      </c>
+      <c r="H79" t="s">
+        <v>436</v>
+      </c>
+      <c r="I79" t="s">
+        <v>450</v>
+      </c>
+      <c r="J79" t="s">
+        <v>441</v>
+      </c>
+      <c r="K79" t="s">
+        <v>436</v>
+      </c>
+      <c r="L79" t="s">
+        <v>436</v>
+      </c>
+      <c r="M79" t="s">
+        <v>442</v>
+      </c>
+      <c r="N79" t="s">
+        <v>443</v>
+      </c>
+      <c r="O79" t="s">
+        <v>450</v>
+      </c>
+      <c r="P79" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="80" spans="2:17">
+      <c r="B80" t="s">
+        <v>573</v>
+      </c>
+      <c r="C80" t="s">
+        <v>436</v>
+      </c>
+      <c r="D80" t="s">
+        <v>574</v>
+      </c>
+      <c r="E80" t="s">
+        <v>575</v>
+      </c>
+      <c r="F80" t="s">
+        <v>439</v>
+      </c>
+      <c r="G80" t="s">
+        <v>442</v>
+      </c>
+      <c r="H80" t="s">
+        <v>436</v>
+      </c>
+      <c r="I80" t="s">
+        <v>450</v>
+      </c>
+      <c r="J80" t="s">
+        <v>441</v>
+      </c>
+      <c r="K80" t="s">
+        <v>436</v>
+      </c>
+      <c r="L80" t="s">
+        <v>436</v>
+      </c>
+      <c r="M80" t="s">
+        <v>442</v>
+      </c>
+      <c r="N80" t="s">
+        <v>443</v>
+      </c>
+      <c r="O80" t="s">
+        <v>450</v>
+      </c>
+      <c r="P80" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="81" spans="2:17">
+      <c r="B81" t="s">
+        <v>577</v>
+      </c>
+      <c r="C81" t="s">
+        <v>436</v>
+      </c>
+      <c r="D81" t="s">
+        <v>578</v>
+      </c>
+      <c r="E81" t="s">
+        <v>579</v>
+      </c>
+      <c r="F81" t="s">
+        <v>439</v>
+      </c>
+      <c r="G81" t="s">
+        <v>440</v>
+      </c>
+      <c r="H81" t="s">
+        <v>436</v>
+      </c>
+      <c r="I81" t="s">
+        <v>436</v>
+      </c>
+      <c r="J81" t="s">
+        <v>441</v>
+      </c>
+      <c r="K81" t="s">
+        <v>436</v>
+      </c>
+      <c r="L81" t="s">
+        <v>436</v>
+      </c>
+      <c r="M81" t="s">
+        <v>442</v>
+      </c>
+      <c r="N81" t="s">
+        <v>443</v>
+      </c>
+      <c r="O81" t="s">
+        <v>450</v>
+      </c>
+      <c r="P81" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="82" spans="2:17">
+      <c r="B82" t="s">
+        <v>581</v>
+      </c>
+      <c r="C82" t="s">
+        <v>436</v>
+      </c>
+      <c r="D82" t="s">
+        <v>582</v>
+      </c>
+      <c r="E82" t="s">
+        <v>583</v>
+      </c>
+      <c r="F82" t="s">
+        <v>439</v>
+      </c>
+      <c r="G82" t="s">
+        <v>440</v>
+      </c>
+      <c r="H82" t="s">
+        <v>436</v>
+      </c>
+      <c r="I82" t="s">
+        <v>436</v>
+      </c>
+      <c r="J82" t="s">
+        <v>441</v>
+      </c>
+      <c r="K82" t="s">
+        <v>436</v>
+      </c>
+      <c r="L82" t="s">
+        <v>436</v>
+      </c>
+      <c r="M82" t="s">
+        <v>442</v>
+      </c>
+      <c r="N82" t="s">
+        <v>443</v>
+      </c>
+      <c r="O82" t="s">
+        <v>450</v>
+      </c>
+      <c r="P82" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="83" spans="2:17">
+      <c r="B83" t="s">
+        <v>585</v>
+      </c>
+      <c r="C83" t="s">
+        <v>436</v>
+      </c>
+      <c r="D83" t="s">
+        <v>586</v>
+      </c>
+      <c r="E83" t="s">
+        <v>587</v>
+      </c>
+      <c r="F83" t="s">
+        <v>439</v>
+      </c>
+      <c r="G83" t="s">
+        <v>442</v>
+      </c>
+      <c r="H83" t="s">
+        <v>450</v>
+      </c>
+      <c r="I83" t="s">
+        <v>588</v>
+      </c>
+      <c r="J83" t="s">
+        <v>441</v>
+      </c>
+      <c r="K83" t="s">
+        <v>436</v>
+      </c>
+      <c r="L83" t="s">
+        <v>436</v>
+      </c>
+      <c r="M83" t="s">
+        <v>442</v>
+      </c>
+      <c r="N83" t="s">
+        <v>443</v>
+      </c>
+      <c r="O83" t="s">
+        <v>465</v>
+      </c>
+      <c r="P83" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="84" spans="2:17">
+      <c r="B84" t="s">
+        <v>590</v>
+      </c>
+      <c r="C84" t="s">
+        <v>436</v>
+      </c>
+      <c r="D84" t="s">
+        <v>591</v>
+      </c>
+      <c r="E84" t="s">
+        <v>592</v>
+      </c>
+      <c r="F84" t="s">
+        <v>439</v>
+      </c>
+      <c r="G84" t="s">
+        <v>440</v>
+      </c>
+      <c r="H84" t="s">
+        <v>436</v>
+      </c>
+      <c r="I84" t="s">
+        <v>436</v>
+      </c>
+      <c r="J84" t="s">
+        <v>516</v>
+      </c>
+      <c r="K84" t="s">
+        <v>450</v>
+      </c>
+      <c r="L84" t="s">
+        <v>436</v>
+      </c>
+      <c r="M84" t="s">
+        <v>442</v>
+      </c>
+      <c r="N84" t="s">
+        <v>443</v>
+      </c>
+      <c r="O84" t="s">
+        <v>555</v>
+      </c>
+      <c r="P84" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="85" spans="2:17">
+      <c r="B85" t="s">
+        <v>594</v>
+      </c>
+      <c r="C85" t="s">
+        <v>436</v>
+      </c>
+      <c r="D85" t="s">
+        <v>595</v>
+      </c>
+      <c r="E85" t="s">
+        <v>596</v>
+      </c>
+      <c r="F85" t="s">
+        <v>439</v>
+      </c>
+      <c r="G85" t="s">
+        <v>440</v>
+      </c>
+      <c r="H85" t="s">
+        <v>436</v>
+      </c>
+      <c r="I85" t="s">
+        <v>436</v>
+      </c>
+      <c r="J85" t="s">
+        <v>516</v>
+      </c>
+      <c r="K85" t="s">
+        <v>450</v>
+      </c>
+      <c r="L85" t="s">
+        <v>436</v>
+      </c>
+      <c r="M85" t="s">
+        <v>442</v>
+      </c>
+      <c r="N85" t="s">
+        <v>443</v>
+      </c>
+      <c r="O85" t="s">
+        <v>555</v>
+      </c>
+      <c r="P85" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="86" spans="2:17">
+      <c r="B86" t="s">
+        <v>598</v>
+      </c>
+      <c r="C86" t="s">
+        <v>436</v>
+      </c>
+      <c r="D86" t="s">
+        <v>599</v>
+      </c>
+      <c r="E86" t="s">
+        <v>600</v>
+      </c>
+      <c r="F86" t="s">
+        <v>439</v>
+      </c>
+      <c r="G86" t="s">
+        <v>440</v>
+      </c>
+      <c r="H86" t="s">
+        <v>436</v>
+      </c>
+      <c r="I86" t="s">
+        <v>436</v>
+      </c>
+      <c r="J86" t="s">
+        <v>516</v>
+      </c>
+      <c r="K86" t="s">
+        <v>450</v>
+      </c>
+      <c r="L86" t="s">
+        <v>436</v>
+      </c>
+      <c r="M86" t="s">
+        <v>442</v>
+      </c>
+      <c r="N86" t="s">
+        <v>443</v>
+      </c>
+      <c r="O86" t="s">
+        <v>555</v>
+      </c>
+      <c r="P86" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="87" spans="2:17">
+      <c r="B87" t="s">
+        <v>602</v>
+      </c>
+      <c r="C87" t="s">
+        <v>436</v>
+      </c>
+      <c r="D87" t="s">
+        <v>603</v>
+      </c>
+      <c r="E87" t="s">
+        <v>604</v>
+      </c>
+      <c r="F87" t="s">
+        <v>439</v>
+      </c>
+      <c r="G87" t="s">
+        <v>442</v>
+      </c>
+      <c r="H87" t="s">
+        <v>436</v>
+      </c>
+      <c r="I87" t="s">
+        <v>605</v>
+      </c>
+      <c r="J87" t="s">
+        <v>606</v>
+      </c>
+      <c r="K87" t="s">
+        <v>436</v>
+      </c>
+      <c r="L87" t="s">
+        <v>436</v>
+      </c>
+      <c r="M87" t="s">
+        <v>442</v>
+      </c>
+      <c r="N87" t="s">
+        <v>443</v>
+      </c>
+      <c r="O87" t="s">
+        <v>465</v>
+      </c>
+      <c r="P87" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="88" spans="2:17">
+      <c r="B88" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C88" t="s">
+        <v>436</v>
+      </c>
+      <c r="D88" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E88" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F88" t="s">
+        <v>439</v>
+      </c>
+      <c r="G88" t="s">
+        <v>440</v>
+      </c>
+      <c r="H88" t="s">
+        <v>436</v>
+      </c>
+      <c r="I88" t="s">
+        <v>436</v>
+      </c>
+      <c r="J88" t="s">
+        <v>516</v>
+      </c>
+      <c r="K88" t="s">
+        <v>450</v>
+      </c>
+      <c r="L88" t="s">
+        <v>436</v>
+      </c>
+      <c r="M88" t="s">
+        <v>442</v>
+      </c>
+      <c r="N88" t="s">
+        <v>443</v>
+      </c>
+      <c r="O88" t="s">
+        <v>555</v>
+      </c>
+      <c r="P88" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="89" spans="2:17">
+      <c r="B89" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C89" t="s">
+        <v>436</v>
+      </c>
+      <c r="D89" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E89" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F89" t="s">
+        <v>439</v>
+      </c>
+      <c r="G89" t="s">
+        <v>440</v>
+      </c>
+      <c r="H89" t="s">
+        <v>436</v>
+      </c>
+      <c r="I89" t="s">
+        <v>436</v>
+      </c>
+      <c r="J89" t="s">
+        <v>516</v>
+      </c>
+      <c r="K89" t="s">
+        <v>450</v>
+      </c>
+      <c r="L89" t="s">
+        <v>436</v>
+      </c>
+      <c r="M89" t="s">
+        <v>442</v>
+      </c>
+      <c r="N89" t="s">
+        <v>443</v>
+      </c>
+      <c r="O89" t="s">
+        <v>555</v>
+      </c>
+      <c r="P89" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="90" spans="2:17">
+      <c r="B90" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C90" t="s">
+        <v>436</v>
+      </c>
+      <c r="D90" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E90" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F90" t="s">
+        <v>439</v>
+      </c>
+      <c r="G90" t="s">
+        <v>440</v>
+      </c>
+      <c r="H90" t="s">
+        <v>436</v>
+      </c>
+      <c r="I90" t="s">
+        <v>436</v>
+      </c>
+      <c r="J90" t="s">
+        <v>441</v>
+      </c>
+      <c r="K90" t="s">
+        <v>436</v>
+      </c>
+      <c r="L90" t="s">
+        <v>436</v>
+      </c>
+      <c r="M90" t="s">
+        <v>440</v>
+      </c>
+      <c r="N90" t="s">
+        <v>443</v>
+      </c>
+      <c r="O90" t="s">
+        <v>444</v>
+      </c>
+      <c r="P90" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="91" spans="2:17">
+      <c r="B91" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C91" t="s">
+        <v>436</v>
+      </c>
+      <c r="D91" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E91" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F91" t="s">
+        <v>439</v>
+      </c>
+      <c r="G91" t="s">
+        <v>440</v>
+      </c>
+      <c r="H91" t="s">
+        <v>436</v>
+      </c>
+      <c r="I91" t="s">
+        <v>436</v>
+      </c>
+      <c r="J91" t="s">
+        <v>441</v>
+      </c>
+      <c r="K91" t="s">
+        <v>436</v>
+      </c>
+      <c r="L91" t="s">
+        <v>436</v>
+      </c>
+      <c r="M91" t="s">
+        <v>440</v>
+      </c>
+      <c r="N91" t="s">
+        <v>443</v>
+      </c>
+      <c r="O91" t="s">
+        <v>444</v>
+      </c>
+      <c r="P91" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="93" spans="2:17">
+      <c r="B93" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C93" t="s">
+        <v>436</v>
+      </c>
+      <c r="D93" t="s">
+        <v>736</v>
+      </c>
+      <c r="E93" t="s">
+        <v>737</v>
+      </c>
+      <c r="F93" t="s">
+        <v>439</v>
+      </c>
+      <c r="G93" t="s">
+        <v>440</v>
+      </c>
+      <c r="H93" t="s">
+        <v>436</v>
+      </c>
+      <c r="I93" t="s">
+        <v>436</v>
+      </c>
+      <c r="J93" t="s">
+        <v>808</v>
+      </c>
+      <c r="K93" t="s">
+        <v>450</v>
+      </c>
+      <c r="L93" t="s">
+        <v>436</v>
+      </c>
+      <c r="M93" t="s">
+        <v>442</v>
+      </c>
+      <c r="N93" t="s">
+        <v>443</v>
+      </c>
+      <c r="O93" t="s">
+        <v>456</v>
+      </c>
+      <c r="P93" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="94" spans="2:17">
+      <c r="B94" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C94" t="s">
+        <v>436</v>
+      </c>
+      <c r="D94" t="s">
+        <v>740</v>
+      </c>
+      <c r="E94" t="s">
+        <v>741</v>
+      </c>
+      <c r="F94" t="s">
+        <v>439</v>
+      </c>
+      <c r="G94" t="s">
+        <v>440</v>
+      </c>
+      <c r="H94" t="s">
+        <v>436</v>
+      </c>
+      <c r="I94" t="s">
+        <v>436</v>
+      </c>
+      <c r="J94" t="s">
+        <v>808</v>
+      </c>
+      <c r="K94" t="s">
+        <v>450</v>
+      </c>
+      <c r="L94" t="s">
+        <v>436</v>
+      </c>
+      <c r="M94" t="s">
+        <v>442</v>
+      </c>
+      <c r="N94" t="s">
+        <v>443</v>
+      </c>
+      <c r="O94" t="s">
+        <v>456</v>
+      </c>
+      <c r="P94" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="95" spans="2:17">
+      <c r="B95" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C95" t="s">
+        <v>436</v>
+      </c>
+      <c r="D95" t="s">
+        <v>744</v>
+      </c>
+      <c r="E95" t="s">
+        <v>745</v>
+      </c>
+      <c r="F95" t="s">
+        <v>439</v>
+      </c>
+      <c r="G95" t="s">
+        <v>440</v>
+      </c>
+      <c r="H95" t="s">
+        <v>436</v>
+      </c>
+      <c r="I95" t="s">
+        <v>436</v>
+      </c>
+      <c r="J95" t="s">
+        <v>808</v>
+      </c>
+      <c r="K95" t="s">
+        <v>450</v>
+      </c>
+      <c r="L95" t="s">
+        <v>436</v>
+      </c>
+      <c r="M95" t="s">
+        <v>442</v>
+      </c>
+      <c r="N95" t="s">
+        <v>443</v>
+      </c>
+      <c r="O95" t="s">
+        <v>456</v>
+      </c>
+      <c r="P95" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="96" spans="2:17">
+      <c r="B96" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C96" t="s">
+        <v>436</v>
+      </c>
+      <c r="D96" t="s">
+        <v>748</v>
+      </c>
+      <c r="E96" t="s">
+        <v>749</v>
+      </c>
+      <c r="F96" t="s">
+        <v>439</v>
+      </c>
+      <c r="G96" t="s">
+        <v>440</v>
+      </c>
+      <c r="H96" t="s">
+        <v>436</v>
+      </c>
+      <c r="I96" t="s">
+        <v>436</v>
+      </c>
+      <c r="J96" t="s">
+        <v>516</v>
+      </c>
+      <c r="K96" t="s">
+        <v>450</v>
+      </c>
+      <c r="L96" t="s">
+        <v>436</v>
+      </c>
+      <c r="M96" t="s">
+        <v>442</v>
+      </c>
+      <c r="N96" t="s">
+        <v>443</v>
+      </c>
+      <c r="O96" t="s">
+        <v>456</v>
+      </c>
+      <c r="P96" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="97" spans="2:17">
+      <c r="B97" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C97" t="s">
+        <v>436</v>
+      </c>
+      <c r="D97" t="s">
+        <v>1052</v>
+      </c>
+      <c r="E97" t="s">
+        <v>1053</v>
+      </c>
+      <c r="F97" t="s">
+        <v>439</v>
+      </c>
+      <c r="G97" t="s">
+        <v>440</v>
+      </c>
+      <c r="H97" t="s">
+        <v>436</v>
+      </c>
+      <c r="I97" t="s">
+        <v>436</v>
+      </c>
+      <c r="J97" t="s">
+        <v>441</v>
+      </c>
+      <c r="K97" t="s">
+        <v>436</v>
+      </c>
+      <c r="L97" t="s">
+        <v>436</v>
+      </c>
+      <c r="M97" t="s">
+        <v>440</v>
+      </c>
+      <c r="N97" t="s">
+        <v>443</v>
+      </c>
+      <c r="O97" t="s">
+        <v>444</v>
+      </c>
+      <c r="P97" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="98" spans="2:17">
+      <c r="B98" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C98" t="s">
+        <v>436</v>
+      </c>
+      <c r="D98" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E98" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F98" t="s">
+        <v>439</v>
+      </c>
+      <c r="G98" t="s">
+        <v>440</v>
+      </c>
+      <c r="H98" t="s">
+        <v>436</v>
+      </c>
+      <c r="I98" t="s">
+        <v>436</v>
+      </c>
+      <c r="J98" t="s">
+        <v>441</v>
+      </c>
+      <c r="K98" t="s">
+        <v>436</v>
+      </c>
+      <c r="L98" t="s">
+        <v>436</v>
+      </c>
+      <c r="M98" t="s">
+        <v>440</v>
+      </c>
+      <c r="N98" t="s">
+        <v>443</v>
+      </c>
+      <c r="O98" t="s">
+        <v>444</v>
+      </c>
+      <c r="P98" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="100" spans="2:17">
+      <c r="B100" t="s">
+        <v>644</v>
+      </c>
+      <c r="C100" t="s">
+        <v>436</v>
+      </c>
+      <c r="D100" t="s">
+        <v>645</v>
+      </c>
+      <c r="E100" t="s">
+        <v>646</v>
+      </c>
+      <c r="F100" t="s">
+        <v>439</v>
+      </c>
+      <c r="G100" t="s">
+        <v>440</v>
+      </c>
+      <c r="H100" t="s">
+        <v>436</v>
+      </c>
+      <c r="I100" t="s">
+        <v>436</v>
+      </c>
+      <c r="J100" t="s">
+        <v>441</v>
+      </c>
+      <c r="K100" t="s">
+        <v>450</v>
+      </c>
+      <c r="L100" t="s">
+        <v>436</v>
+      </c>
+      <c r="M100" t="s">
+        <v>442</v>
+      </c>
+      <c r="N100" t="s">
+        <v>443</v>
+      </c>
+      <c r="O100" t="s">
+        <v>562</v>
+      </c>
+      <c r="P100" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="101" spans="2:17">
+      <c r="B101" t="s">
+        <v>648</v>
+      </c>
+      <c r="C101" t="s">
+        <v>436</v>
+      </c>
+      <c r="D101" t="s">
+        <v>649</v>
+      </c>
+      <c r="E101" t="s">
+        <v>650</v>
+      </c>
+      <c r="F101" t="s">
+        <v>439</v>
+      </c>
+      <c r="G101" t="s">
+        <v>440</v>
+      </c>
+      <c r="H101" t="s">
+        <v>436</v>
+      </c>
+      <c r="I101" t="s">
+        <v>436</v>
+      </c>
+      <c r="J101" t="s">
+        <v>441</v>
+      </c>
+      <c r="K101" t="s">
+        <v>450</v>
+      </c>
+      <c r="L101" t="s">
+        <v>436</v>
+      </c>
+      <c r="M101" t="s">
+        <v>442</v>
+      </c>
+      <c r="N101" t="s">
+        <v>443</v>
+      </c>
+      <c r="O101" t="s">
+        <v>562</v>
+      </c>
+      <c r="P101" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="102" spans="2:17">
+      <c r="B102" t="s">
+        <v>652</v>
+      </c>
+      <c r="C102" t="s">
+        <v>436</v>
+      </c>
+      <c r="D102" t="s">
+        <v>653</v>
+      </c>
+      <c r="E102" t="s">
+        <v>654</v>
+      </c>
+      <c r="F102" t="s">
+        <v>439</v>
+      </c>
+      <c r="G102" t="s">
+        <v>440</v>
+      </c>
+      <c r="H102" t="s">
+        <v>436</v>
+      </c>
+      <c r="I102" t="s">
+        <v>436</v>
+      </c>
+      <c r="J102" t="s">
+        <v>441</v>
+      </c>
+      <c r="K102" t="s">
+        <v>450</v>
+      </c>
+      <c r="L102" t="s">
+        <v>436</v>
+      </c>
+      <c r="M102" t="s">
+        <v>442</v>
+      </c>
+      <c r="N102" t="s">
+        <v>443</v>
+      </c>
+      <c r="O102" t="s">
+        <v>562</v>
+      </c>
+      <c r="P102" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="103" spans="2:17">
+      <c r="B103" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C103" t="s">
+        <v>436</v>
+      </c>
+      <c r="D103" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E103" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F103" t="s">
+        <v>439</v>
+      </c>
+      <c r="G103" t="s">
+        <v>440</v>
+      </c>
+      <c r="H103" t="s">
+        <v>436</v>
+      </c>
+      <c r="I103" t="s">
+        <v>436</v>
+      </c>
+      <c r="J103" t="s">
+        <v>441</v>
+      </c>
+      <c r="K103" t="s">
+        <v>436</v>
+      </c>
+      <c r="L103" t="s">
+        <v>436</v>
+      </c>
+      <c r="M103" t="s">
+        <v>440</v>
+      </c>
+      <c r="N103" t="s">
+        <v>443</v>
+      </c>
+      <c r="O103" t="s">
+        <v>444</v>
+      </c>
+      <c r="P103" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="104" spans="2:17">
+      <c r="B104" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C104" t="s">
+        <v>436</v>
+      </c>
+      <c r="D104" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E104" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F104" t="s">
+        <v>439</v>
+      </c>
+      <c r="G104" t="s">
+        <v>440</v>
+      </c>
+      <c r="H104" t="s">
+        <v>436</v>
+      </c>
+      <c r="I104" t="s">
+        <v>436</v>
+      </c>
+      <c r="J104" t="s">
+        <v>441</v>
+      </c>
+      <c r="K104" t="s">
+        <v>436</v>
+      </c>
+      <c r="L104" t="s">
+        <v>436</v>
+      </c>
+      <c r="M104" t="s">
+        <v>440</v>
+      </c>
+      <c r="N104" t="s">
+        <v>443</v>
+      </c>
+      <c r="O104" t="s">
+        <v>444</v>
+      </c>
+      <c r="P104" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="106" spans="2:17">
+      <c r="B106" t="s">
+        <v>657</v>
+      </c>
+      <c r="C106" t="s">
+        <v>436</v>
+      </c>
+      <c r="D106" t="s">
+        <v>658</v>
+      </c>
+      <c r="E106" t="s">
+        <v>659</v>
+      </c>
+      <c r="F106" t="s">
+        <v>439</v>
+      </c>
+      <c r="G106" t="s">
+        <v>442</v>
+      </c>
+      <c r="H106" t="s">
+        <v>436</v>
+      </c>
+      <c r="I106" t="s">
+        <v>660</v>
+      </c>
+      <c r="J106" t="s">
+        <v>661</v>
+      </c>
+      <c r="K106" t="s">
+        <v>439</v>
+      </c>
+      <c r="L106" t="s">
+        <v>436</v>
+      </c>
+      <c r="M106" t="s">
+        <v>442</v>
+      </c>
+      <c r="N106" t="s">
+        <v>443</v>
+      </c>
+      <c r="O106" t="s">
+        <v>555</v>
+      </c>
+      <c r="P106" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="107" spans="2:17">
+      <c r="B107" t="s">
+        <v>663</v>
+      </c>
+      <c r="C107" t="s">
+        <v>436</v>
+      </c>
+      <c r="D107" t="s">
+        <v>664</v>
+      </c>
+      <c r="E107" t="s">
+        <v>665</v>
+      </c>
+      <c r="F107" t="s">
+        <v>439</v>
+      </c>
+      <c r="G107" t="s">
+        <v>442</v>
+      </c>
+      <c r="H107" t="s">
+        <v>436</v>
+      </c>
+      <c r="I107" t="s">
+        <v>660</v>
+      </c>
+      <c r="J107" t="s">
+        <v>661</v>
+      </c>
+      <c r="K107" t="s">
+        <v>439</v>
+      </c>
+      <c r="L107" t="s">
+        <v>436</v>
+      </c>
+      <c r="M107" t="s">
+        <v>442</v>
+      </c>
+      <c r="N107" t="s">
+        <v>443</v>
+      </c>
+      <c r="O107" t="s">
+        <v>555</v>
+      </c>
+      <c r="P107" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="108" spans="2:17">
+      <c r="B108" t="s">
+        <v>667</v>
+      </c>
+      <c r="C108" t="s">
+        <v>436</v>
+      </c>
+      <c r="D108" t="s">
+        <v>668</v>
+      </c>
+      <c r="E108" t="s">
+        <v>669</v>
+      </c>
+      <c r="F108" t="s">
+        <v>439</v>
+      </c>
+      <c r="G108" t="s">
+        <v>442</v>
+      </c>
+      <c r="H108" t="s">
+        <v>436</v>
+      </c>
+      <c r="I108" t="s">
+        <v>660</v>
+      </c>
+      <c r="J108" t="s">
+        <v>661</v>
+      </c>
+      <c r="K108" t="s">
+        <v>439</v>
+      </c>
+      <c r="L108" t="s">
+        <v>436</v>
+      </c>
+      <c r="M108" t="s">
+        <v>442</v>
+      </c>
+      <c r="N108" t="s">
+        <v>443</v>
+      </c>
+      <c r="O108" t="s">
+        <v>555</v>
+      </c>
+      <c r="P108" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="109" spans="2:17">
+      <c r="B109" t="s">
+        <v>671</v>
+      </c>
+      <c r="C109" t="s">
+        <v>436</v>
+      </c>
+      <c r="D109" t="s">
+        <v>672</v>
+      </c>
+      <c r="E109" t="s">
+        <v>673</v>
+      </c>
+      <c r="F109" t="s">
+        <v>439</v>
+      </c>
+      <c r="G109" t="s">
+        <v>442</v>
+      </c>
+      <c r="H109" t="s">
+        <v>436</v>
+      </c>
+      <c r="I109" t="s">
+        <v>660</v>
+      </c>
+      <c r="J109" t="s">
+        <v>661</v>
+      </c>
+      <c r="K109" t="s">
+        <v>439</v>
+      </c>
+      <c r="L109" t="s">
+        <v>436</v>
+      </c>
+      <c r="M109" t="s">
+        <v>442</v>
+      </c>
+      <c r="N109" t="s">
+        <v>443</v>
+      </c>
+      <c r="O109" t="s">
+        <v>555</v>
+      </c>
+      <c r="P109" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="110" spans="2:17">
+      <c r="B110" t="s">
+        <v>675</v>
+      </c>
+      <c r="C110" t="s">
+        <v>436</v>
+      </c>
+      <c r="D110" t="s">
+        <v>676</v>
+      </c>
+      <c r="E110" t="s">
+        <v>677</v>
+      </c>
+      <c r="F110" t="s">
+        <v>439</v>
+      </c>
+      <c r="G110" t="s">
+        <v>442</v>
+      </c>
+      <c r="H110" t="s">
+        <v>436</v>
+      </c>
+      <c r="I110" t="s">
+        <v>660</v>
+      </c>
+      <c r="J110" t="s">
+        <v>661</v>
+      </c>
+      <c r="K110" t="s">
+        <v>439</v>
+      </c>
+      <c r="L110" t="s">
+        <v>436</v>
+      </c>
+      <c r="M110" t="s">
+        <v>442</v>
+      </c>
+      <c r="N110" t="s">
+        <v>443</v>
+      </c>
+      <c r="O110" t="s">
+        <v>555</v>
+      </c>
+      <c r="P110" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="111" spans="2:17">
+      <c r="B111" t="s">
+        <v>679</v>
+      </c>
+      <c r="C111" t="s">
+        <v>436</v>
+      </c>
+      <c r="D111" t="s">
+        <v>680</v>
+      </c>
+      <c r="E111" t="s">
+        <v>681</v>
+      </c>
+      <c r="F111" t="s">
+        <v>439</v>
+      </c>
+      <c r="G111" t="s">
+        <v>442</v>
+      </c>
+      <c r="H111" t="s">
+        <v>436</v>
+      </c>
+      <c r="I111" t="s">
+        <v>660</v>
+      </c>
+      <c r="J111" t="s">
+        <v>661</v>
+      </c>
+      <c r="K111" t="s">
+        <v>439</v>
+      </c>
+      <c r="L111" t="s">
+        <v>436</v>
+      </c>
+      <c r="M111" t="s">
+        <v>442</v>
+      </c>
+      <c r="N111" t="s">
+        <v>443</v>
+      </c>
+      <c r="O111" t="s">
+        <v>555</v>
+      </c>
+      <c r="P111" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="112" spans="2:17">
+      <c r="B112" t="s">
+        <v>683</v>
+      </c>
+      <c r="C112" t="s">
+        <v>436</v>
+      </c>
+      <c r="D112" t="s">
+        <v>684</v>
+      </c>
+      <c r="E112" t="s">
+        <v>685</v>
+      </c>
+      <c r="F112" t="s">
+        <v>439</v>
+      </c>
+      <c r="G112" t="s">
+        <v>442</v>
+      </c>
+      <c r="H112" t="s">
+        <v>436</v>
+      </c>
+      <c r="I112" t="s">
+        <v>660</v>
+      </c>
+      <c r="J112" t="s">
+        <v>661</v>
+      </c>
+      <c r="K112" t="s">
+        <v>439</v>
+      </c>
+      <c r="L112" t="s">
+        <v>436</v>
+      </c>
+      <c r="M112" t="s">
+        <v>442</v>
+      </c>
+      <c r="N112" t="s">
+        <v>443</v>
+      </c>
+      <c r="O112" t="s">
+        <v>555</v>
+      </c>
+      <c r="P112" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="113" spans="2:17">
+      <c r="B113" t="s">
+        <v>687</v>
+      </c>
+      <c r="C113" t="s">
+        <v>436</v>
+      </c>
+      <c r="D113" t="s">
+        <v>688</v>
+      </c>
+      <c r="E113" t="s">
+        <v>689</v>
+      </c>
+      <c r="F113" t="s">
+        <v>439</v>
+      </c>
+      <c r="G113" t="s">
+        <v>442</v>
+      </c>
+      <c r="H113" t="s">
+        <v>436</v>
+      </c>
+      <c r="I113" t="s">
+        <v>660</v>
+      </c>
+      <c r="J113" t="s">
+        <v>661</v>
+      </c>
+      <c r="K113" t="s">
+        <v>439</v>
+      </c>
+      <c r="L113" t="s">
+        <v>436</v>
+      </c>
+      <c r="M113" t="s">
+        <v>442</v>
+      </c>
+      <c r="N113" t="s">
+        <v>443</v>
+      </c>
+      <c r="O113" t="s">
+        <v>555</v>
+      </c>
+      <c r="P113" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="114" spans="2:17">
+      <c r="B114" t="s">
+        <v>691</v>
+      </c>
+      <c r="C114" t="s">
+        <v>436</v>
+      </c>
+      <c r="D114" t="s">
+        <v>692</v>
+      </c>
+      <c r="E114" t="s">
+        <v>693</v>
+      </c>
+      <c r="F114" t="s">
+        <v>439</v>
+      </c>
+      <c r="G114" t="s">
+        <v>442</v>
+      </c>
+      <c r="H114" t="s">
+        <v>436</v>
+      </c>
+      <c r="I114" t="s">
+        <v>660</v>
+      </c>
+      <c r="J114" t="s">
+        <v>661</v>
+      </c>
+      <c r="K114" t="s">
+        <v>439</v>
+      </c>
+      <c r="L114" t="s">
+        <v>436</v>
+      </c>
+      <c r="M114" t="s">
+        <v>442</v>
+      </c>
+      <c r="N114" t="s">
+        <v>443</v>
+      </c>
+      <c r="O114" t="s">
+        <v>555</v>
+      </c>
+      <c r="P114" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="115" spans="2:17">
+      <c r="B115" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C115" t="s">
+        <v>436</v>
+      </c>
+      <c r="D115" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E115" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F115" t="s">
+        <v>439</v>
+      </c>
+      <c r="G115" t="s">
+        <v>440</v>
+      </c>
+      <c r="H115" t="s">
+        <v>436</v>
+      </c>
+      <c r="I115" t="s">
+        <v>436</v>
+      </c>
+      <c r="J115" t="s">
+        <v>441</v>
+      </c>
+      <c r="K115" t="s">
+        <v>436</v>
+      </c>
+      <c r="L115" t="s">
+        <v>436</v>
+      </c>
+      <c r="M115" t="s">
+        <v>440</v>
+      </c>
+      <c r="N115" t="s">
+        <v>443</v>
+      </c>
+      <c r="O115" t="s">
+        <v>444</v>
+      </c>
+      <c r="P115" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="116" spans="2:17">
+      <c r="B116" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C116" t="s">
+        <v>436</v>
+      </c>
+      <c r="D116" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E116" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F116" t="s">
+        <v>439</v>
+      </c>
+      <c r="G116" t="s">
+        <v>440</v>
+      </c>
+      <c r="H116" t="s">
+        <v>436</v>
+      </c>
+      <c r="I116" t="s">
+        <v>436</v>
+      </c>
+      <c r="J116" t="s">
+        <v>441</v>
+      </c>
+      <c r="K116" t="s">
+        <v>436</v>
+      </c>
+      <c r="L116" t="s">
+        <v>436</v>
+      </c>
+      <c r="M116" t="s">
+        <v>440</v>
+      </c>
+      <c r="N116" t="s">
+        <v>443</v>
+      </c>
+      <c r="O116" t="s">
+        <v>444</v>
+      </c>
+      <c r="P116" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="118" spans="2:17">
+      <c r="B118" t="s">
+        <v>519</v>
+      </c>
+      <c r="C118" t="s">
+        <v>436</v>
+      </c>
+      <c r="D118" t="s">
+        <v>520</v>
+      </c>
+      <c r="E118" t="s">
+        <v>521</v>
+      </c>
+      <c r="F118" t="s">
+        <v>439</v>
+      </c>
+      <c r="G118" t="s">
+        <v>440</v>
+      </c>
+      <c r="H118" t="s">
+        <v>436</v>
+      </c>
+      <c r="I118" t="s">
+        <v>436</v>
+      </c>
+      <c r="J118" t="s">
+        <v>516</v>
+      </c>
+      <c r="K118" t="s">
+        <v>450</v>
+      </c>
+      <c r="L118" t="s">
+        <v>436</v>
+      </c>
+      <c r="M118" t="s">
+        <v>442</v>
+      </c>
+      <c r="N118" t="s">
+        <v>443</v>
+      </c>
+      <c r="O118" t="s">
+        <v>456</v>
+      </c>
+      <c r="P118" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="119" spans="2:17">
+      <c r="B119" t="s">
+        <v>526</v>
+      </c>
+      <c r="C119" t="s">
+        <v>436</v>
+      </c>
+      <c r="D119" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E119" t="s">
+        <v>528</v>
+      </c>
+      <c r="F119" t="s">
+        <v>439</v>
+      </c>
+      <c r="G119" t="s">
+        <v>440</v>
+      </c>
+      <c r="H119" t="s">
+        <v>436</v>
+      </c>
+      <c r="I119" t="s">
+        <v>436</v>
+      </c>
+      <c r="J119" t="s">
+        <v>516</v>
+      </c>
+      <c r="K119" t="s">
+        <v>450</v>
+      </c>
+      <c r="L119" t="s">
+        <v>436</v>
+      </c>
+      <c r="M119" t="s">
+        <v>442</v>
+      </c>
+      <c r="N119" t="s">
+        <v>443</v>
+      </c>
+      <c r="O119" t="s">
+        <v>456</v>
+      </c>
+      <c r="P119" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="120" spans="2:17">
+      <c r="B120" t="s">
+        <v>530</v>
+      </c>
+      <c r="C120" t="s">
+        <v>436</v>
+      </c>
+      <c r="D120" t="s">
+        <v>531</v>
+      </c>
+      <c r="E120" t="s">
+        <v>532</v>
+      </c>
+      <c r="F120" t="s">
+        <v>439</v>
+      </c>
+      <c r="G120" t="s">
+        <v>440</v>
+      </c>
+      <c r="H120" t="s">
+        <v>436</v>
+      </c>
+      <c r="I120" t="s">
+        <v>436</v>
+      </c>
+      <c r="J120" t="s">
+        <v>516</v>
+      </c>
+      <c r="K120" t="s">
+        <v>450</v>
+      </c>
+      <c r="L120" t="s">
+        <v>436</v>
+      </c>
+      <c r="M120" t="s">
+        <v>442</v>
+      </c>
+      <c r="N120" t="s">
+        <v>443</v>
+      </c>
+      <c r="O120" t="s">
+        <v>451</v>
+      </c>
+      <c r="P120" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="121" spans="2:17">
+      <c r="B121" t="s">
+        <v>534</v>
+      </c>
+      <c r="C121" t="s">
+        <v>436</v>
+      </c>
+      <c r="D121" t="s">
+        <v>535</v>
+      </c>
+      <c r="E121" t="s">
+        <v>536</v>
+      </c>
+      <c r="F121" t="s">
+        <v>439</v>
+      </c>
+      <c r="G121" t="s">
+        <v>440</v>
+      </c>
+      <c r="H121" t="s">
+        <v>436</v>
+      </c>
+      <c r="I121" t="s">
+        <v>436</v>
+      </c>
+      <c r="J121" t="s">
+        <v>516</v>
+      </c>
+      <c r="K121" t="s">
+        <v>450</v>
+      </c>
+      <c r="L121" t="s">
+        <v>436</v>
+      </c>
+      <c r="M121" t="s">
+        <v>442</v>
+      </c>
+      <c r="N121" t="s">
+        <v>443</v>
+      </c>
+      <c r="O121" t="s">
+        <v>451</v>
+      </c>
+      <c r="P121" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="122" spans="2:17">
+      <c r="B122" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C122" t="s">
+        <v>436</v>
+      </c>
+      <c r="D122" t="s">
+        <v>1077</v>
+      </c>
+      <c r="E122" t="s">
+        <v>540</v>
+      </c>
+      <c r="F122" t="s">
+        <v>439</v>
+      </c>
+      <c r="G122" t="s">
+        <v>440</v>
+      </c>
+      <c r="H122" t="s">
+        <v>436</v>
+      </c>
+      <c r="I122" t="s">
+        <v>436</v>
+      </c>
+      <c r="J122" t="s">
+        <v>516</v>
+      </c>
+      <c r="K122" t="s">
+        <v>450</v>
+      </c>
+      <c r="L122" t="s">
+        <v>436</v>
+      </c>
+      <c r="M122" t="s">
+        <v>442</v>
+      </c>
+      <c r="N122" t="s">
+        <v>443</v>
+      </c>
+      <c r="O122" t="s">
+        <v>451</v>
+      </c>
+      <c r="P122" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="123" spans="2:17">
+      <c r="B123" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C123" t="s">
+        <v>436</v>
+      </c>
+      <c r="D123" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E123" t="s">
+        <v>544</v>
+      </c>
+      <c r="F123" t="s">
+        <v>439</v>
+      </c>
+      <c r="G123" t="s">
+        <v>440</v>
+      </c>
+      <c r="H123" t="s">
+        <v>436</v>
+      </c>
+      <c r="I123" t="s">
+        <v>436</v>
+      </c>
+      <c r="J123" t="s">
+        <v>516</v>
+      </c>
+      <c r="K123" t="s">
+        <v>450</v>
+      </c>
+      <c r="L123" t="s">
+        <v>436</v>
+      </c>
+      <c r="M123" t="s">
+        <v>442</v>
+      </c>
+      <c r="N123" t="s">
+        <v>443</v>
+      </c>
+      <c r="O123" t="s">
+        <v>456</v>
+      </c>
+      <c r="P123" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="124" spans="2:17">
+      <c r="B124" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C124" t="s">
+        <v>436</v>
+      </c>
+      <c r="D124" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E124" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F124" t="s">
+        <v>439</v>
+      </c>
+      <c r="G124" t="s">
+        <v>440</v>
+      </c>
+      <c r="H124" t="s">
+        <v>436</v>
+      </c>
+      <c r="I124" t="s">
+        <v>436</v>
+      </c>
+      <c r="J124" t="s">
+        <v>441</v>
+      </c>
+      <c r="K124" t="s">
+        <v>436</v>
+      </c>
+      <c r="L124" t="s">
+        <v>436</v>
+      </c>
+      <c r="M124" t="s">
+        <v>440</v>
+      </c>
+      <c r="N124" t="s">
+        <v>443</v>
+      </c>
+      <c r="O124" t="s">
+        <v>444</v>
+      </c>
+      <c r="P124" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="125" spans="2:17">
+      <c r="B125" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C125" t="s">
+        <v>436</v>
+      </c>
+      <c r="D125" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E125" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F125" t="s">
+        <v>439</v>
+      </c>
+      <c r="G125" t="s">
+        <v>440</v>
+      </c>
+      <c r="H125" t="s">
+        <v>436</v>
+      </c>
+      <c r="I125" t="s">
+        <v>436</v>
+      </c>
+      <c r="J125" t="s">
+        <v>441</v>
+      </c>
+      <c r="K125" t="s">
+        <v>436</v>
+      </c>
+      <c r="L125" t="s">
+        <v>436</v>
+      </c>
+      <c r="M125" t="s">
+        <v>440</v>
+      </c>
+      <c r="N125" t="s">
+        <v>443</v>
+      </c>
+      <c r="O125" t="s">
+        <v>444</v>
+      </c>
+      <c r="P125" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="127" spans="2:17">
+      <c r="B127" t="s">
+        <v>757</v>
+      </c>
+      <c r="C127" t="s">
+        <v>436</v>
+      </c>
+      <c r="D127" t="s">
+        <v>758</v>
+      </c>
+      <c r="E127" t="s">
+        <v>759</v>
+      </c>
+      <c r="F127" t="s">
+        <v>439</v>
+      </c>
+      <c r="G127" t="s">
+        <v>440</v>
+      </c>
+      <c r="H127" t="s">
+        <v>436</v>
+      </c>
+      <c r="I127" t="s">
+        <v>436</v>
+      </c>
+      <c r="J127" t="s">
+        <v>441</v>
+      </c>
+      <c r="K127" t="s">
+        <v>436</v>
+      </c>
+      <c r="L127" t="s">
+        <v>436</v>
+      </c>
+      <c r="M127" t="s">
+        <v>440</v>
+      </c>
+      <c r="N127" t="s">
+        <v>443</v>
+      </c>
+      <c r="O127" t="s">
+        <v>562</v>
+      </c>
+      <c r="P127" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="128" spans="2:17">
+      <c r="B128" t="s">
+        <v>761</v>
+      </c>
+      <c r="C128" t="s">
+        <v>436</v>
+      </c>
+      <c r="D128" t="s">
+        <v>762</v>
+      </c>
+      <c r="E128" t="s">
+        <v>763</v>
+      </c>
+      <c r="F128" t="s">
+        <v>439</v>
+      </c>
+      <c r="G128" t="s">
+        <v>440</v>
+      </c>
+      <c r="H128" t="s">
+        <v>436</v>
+      </c>
+      <c r="I128" t="s">
+        <v>436</v>
+      </c>
+      <c r="J128" t="s">
+        <v>441</v>
+      </c>
+      <c r="K128" t="s">
+        <v>436</v>
+      </c>
+      <c r="L128" t="s">
+        <v>436</v>
+      </c>
+      <c r="M128" t="s">
+        <v>440</v>
+      </c>
+      <c r="N128" t="s">
+        <v>443</v>
+      </c>
+      <c r="O128" t="s">
+        <v>562</v>
+      </c>
+      <c r="P128" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="129" spans="2:17">
+      <c r="B129" t="s">
+        <v>765</v>
+      </c>
+      <c r="C129" t="s">
+        <v>436</v>
+      </c>
+      <c r="D129" t="s">
+        <v>766</v>
+      </c>
+      <c r="E129" t="s">
+        <v>767</v>
+      </c>
+      <c r="F129" t="s">
+        <v>439</v>
+      </c>
+      <c r="G129" t="s">
+        <v>440</v>
+      </c>
+      <c r="H129" t="s">
+        <v>436</v>
+      </c>
+      <c r="I129" t="s">
+        <v>436</v>
+      </c>
+      <c r="J129" t="s">
+        <v>441</v>
+      </c>
+      <c r="K129" t="s">
+        <v>436</v>
+      </c>
+      <c r="L129" t="s">
+        <v>436</v>
+      </c>
+      <c r="M129" t="s">
+        <v>440</v>
+      </c>
+      <c r="N129" t="s">
+        <v>443</v>
+      </c>
+      <c r="O129" t="s">
+        <v>444</v>
+      </c>
+      <c r="P129" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="130" spans="2:17">
+      <c r="B130" t="s">
+        <v>696</v>
+      </c>
+      <c r="C130" t="s">
+        <v>436</v>
+      </c>
+      <c r="D130" t="s">
+        <v>697</v>
+      </c>
+      <c r="E130" t="s">
+        <v>698</v>
+      </c>
+      <c r="F130" t="s">
+        <v>439</v>
+      </c>
+      <c r="G130" t="s">
+        <v>440</v>
+      </c>
+      <c r="H130" t="s">
+        <v>436</v>
+      </c>
+      <c r="I130" t="s">
+        <v>436</v>
+      </c>
+      <c r="J130" t="s">
+        <v>441</v>
+      </c>
+      <c r="K130" t="s">
+        <v>436</v>
+      </c>
+      <c r="L130" t="s">
+        <v>436</v>
+      </c>
+      <c r="M130" t="s">
+        <v>440</v>
+      </c>
+      <c r="N130" t="s">
+        <v>443</v>
+      </c>
+      <c r="O130" t="s">
+        <v>444</v>
+      </c>
+      <c r="P130" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="132" spans="2:17">
+      <c r="B132" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="133" spans="2:17">
+      <c r="B133" t="s">
+        <v>770</v>
+      </c>
+      <c r="C133" t="s">
+        <v>436</v>
+      </c>
+      <c r="D133" t="s">
+        <v>771</v>
+      </c>
+      <c r="E133" t="s">
+        <v>772</v>
+      </c>
+      <c r="F133" t="s">
+        <v>439</v>
+      </c>
+      <c r="G133" t="s">
+        <v>440</v>
+      </c>
+      <c r="H133" t="s">
+        <v>436</v>
+      </c>
+      <c r="I133" t="s">
+        <v>436</v>
+      </c>
+      <c r="J133" t="s">
+        <v>441</v>
+      </c>
+      <c r="K133" t="s">
+        <v>436</v>
+      </c>
+      <c r="L133" t="s">
+        <v>436</v>
+      </c>
+      <c r="M133" t="s">
+        <v>440</v>
+      </c>
+      <c r="N133" t="s">
+        <v>443</v>
+      </c>
+      <c r="O133" t="s">
+        <v>562</v>
+      </c>
+      <c r="P133" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="134" spans="2:17">
+      <c r="B134" t="s">
+        <v>774</v>
+      </c>
+      <c r="C134" t="s">
+        <v>436</v>
+      </c>
+      <c r="D134" t="s">
+        <v>775</v>
+      </c>
+      <c r="E134" t="s">
+        <v>776</v>
+      </c>
+      <c r="F134" t="s">
+        <v>439</v>
+      </c>
+      <c r="G134" t="s">
+        <v>442</v>
+      </c>
+      <c r="H134" t="s">
+        <v>436</v>
+      </c>
+      <c r="I134" t="s">
+        <v>450</v>
+      </c>
+      <c r="J134" t="s">
+        <v>441</v>
+      </c>
+      <c r="K134" t="s">
+        <v>436</v>
+      </c>
+      <c r="L134" t="s">
+        <v>436</v>
+      </c>
+      <c r="M134" t="s">
+        <v>442</v>
+      </c>
+      <c r="N134" t="s">
+        <v>443</v>
+      </c>
+      <c r="O134" t="s">
+        <v>450</v>
+      </c>
+      <c r="P134" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="136" spans="2:17">
+      <c r="B136" t="s">
+        <v>778</v>
+      </c>
+      <c r="C136" t="s">
+        <v>436</v>
+      </c>
+      <c r="D136" t="s">
+        <v>779</v>
+      </c>
+      <c r="E136" t="s">
+        <v>780</v>
+      </c>
+      <c r="F136" t="s">
+        <v>439</v>
+      </c>
+      <c r="G136" t="s">
+        <v>442</v>
+      </c>
+      <c r="H136" t="s">
+        <v>436</v>
+      </c>
+      <c r="I136" t="s">
+        <v>450</v>
+      </c>
+      <c r="J136" t="s">
+        <v>441</v>
+      </c>
+      <c r="K136" t="s">
+        <v>436</v>
+      </c>
+      <c r="L136" t="s">
+        <v>436</v>
+      </c>
+      <c r="M136" t="s">
+        <v>442</v>
+      </c>
+      <c r="N136" t="s">
+        <v>443</v>
+      </c>
+      <c r="O136" t="s">
+        <v>450</v>
+      </c>
+      <c r="P136" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="137" spans="2:17">
+      <c r="B137" t="s">
+        <v>782</v>
+      </c>
+      <c r="C137" t="s">
+        <v>436</v>
+      </c>
+      <c r="D137" t="s">
+        <v>783</v>
+      </c>
+      <c r="E137" t="s">
+        <v>784</v>
+      </c>
+      <c r="F137" t="s">
+        <v>439</v>
+      </c>
+      <c r="G137" t="s">
+        <v>442</v>
+      </c>
+      <c r="H137" t="s">
+        <v>436</v>
+      </c>
+      <c r="I137" t="s">
+        <v>450</v>
+      </c>
+      <c r="J137" t="s">
+        <v>441</v>
+      </c>
+      <c r="K137" t="s">
+        <v>436</v>
+      </c>
+      <c r="L137" t="s">
+        <v>436</v>
+      </c>
+      <c r="M137" t="s">
+        <v>442</v>
+      </c>
+      <c r="N137" t="s">
+        <v>443</v>
+      </c>
+      <c r="O137" t="s">
+        <v>450</v>
+      </c>
+      <c r="P137" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="138" spans="2:17">
+      <c r="B138" t="s">
+        <v>786</v>
+      </c>
+      <c r="C138" t="s">
+        <v>436</v>
+      </c>
+      <c r="D138" t="s">
+        <v>787</v>
+      </c>
+      <c r="E138" t="s">
+        <v>788</v>
+      </c>
+      <c r="F138" t="s">
+        <v>439</v>
+      </c>
+      <c r="G138" t="s">
+        <v>442</v>
+      </c>
+      <c r="H138" t="s">
+        <v>436</v>
+      </c>
+      <c r="I138" t="s">
+        <v>450</v>
+      </c>
+      <c r="J138" t="s">
+        <v>441</v>
+      </c>
+      <c r="K138" t="s">
+        <v>436</v>
+      </c>
+      <c r="L138" t="s">
+        <v>436</v>
+      </c>
+      <c r="M138" t="s">
+        <v>442</v>
+      </c>
+      <c r="N138" t="s">
+        <v>443</v>
+      </c>
+      <c r="O138" t="s">
+        <v>450</v>
+      </c>
+      <c r="P138" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="139" spans="2:17">
+      <c r="B139" t="s">
+        <v>790</v>
+      </c>
+      <c r="C139" t="s">
+        <v>436</v>
+      </c>
+      <c r="D139" t="s">
+        <v>791</v>
+      </c>
+      <c r="E139" t="s">
+        <v>792</v>
+      </c>
+      <c r="F139" t="s">
+        <v>439</v>
+      </c>
+      <c r="G139" t="s">
+        <v>442</v>
+      </c>
+      <c r="H139" t="s">
+        <v>436</v>
+      </c>
+      <c r="I139" t="s">
+        <v>450</v>
+      </c>
+      <c r="J139" t="s">
+        <v>441</v>
+      </c>
+      <c r="K139" t="s">
+        <v>436</v>
+      </c>
+      <c r="L139" t="s">
+        <v>436</v>
+      </c>
+      <c r="M139" t="s">
+        <v>442</v>
+      </c>
+      <c r="N139" t="s">
+        <v>443</v>
+      </c>
+      <c r="O139" t="s">
+        <v>450</v>
+      </c>
+      <c r="P139" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="141" spans="2:17">
+      <c r="B141" t="s">
+        <v>794</v>
+      </c>
+      <c r="C141" t="s">
+        <v>436</v>
+      </c>
+      <c r="D141" t="s">
+        <v>795</v>
+      </c>
+      <c r="E141" t="s">
+        <v>796</v>
+      </c>
+      <c r="F141" t="s">
+        <v>439</v>
+      </c>
+      <c r="G141" t="s">
+        <v>442</v>
+      </c>
+      <c r="H141" t="s">
+        <v>797</v>
+      </c>
+      <c r="I141" t="s">
+        <v>798</v>
+      </c>
+      <c r="J141" t="s">
+        <v>516</v>
+      </c>
+      <c r="K141" t="s">
+        <v>450</v>
+      </c>
+      <c r="L141" t="s">
+        <v>436</v>
+      </c>
+      <c r="M141" t="s">
+        <v>442</v>
+      </c>
+      <c r="N141" t="s">
+        <v>443</v>
+      </c>
+      <c r="O141" t="s">
+        <v>451</v>
+      </c>
+      <c r="P141" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="142" spans="2:17">
+      <c r="B142" t="s">
+        <v>800</v>
+      </c>
+      <c r="C142" t="s">
+        <v>436</v>
+      </c>
+      <c r="D142" t="s">
+        <v>801</v>
+      </c>
+      <c r="E142" t="s">
+        <v>802</v>
+      </c>
+      <c r="F142" t="s">
+        <v>439</v>
+      </c>
+      <c r="G142" t="s">
+        <v>442</v>
+      </c>
+      <c r="H142" t="s">
+        <v>797</v>
+      </c>
+      <c r="I142" t="s">
+        <v>798</v>
+      </c>
+      <c r="J142" t="s">
+        <v>516</v>
+      </c>
+      <c r="K142" t="s">
+        <v>450</v>
+      </c>
+      <c r="L142" t="s">
+        <v>436</v>
+      </c>
+      <c r="M142" t="s">
+        <v>442</v>
+      </c>
+      <c r="N142" t="s">
+        <v>443</v>
+      </c>
+      <c r="O142" t="s">
+        <v>451</v>
+      </c>
+      <c r="P142" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="143" spans="2:17">
+      <c r="B143" t="s">
+        <v>804</v>
+      </c>
+      <c r="C143" t="s">
+        <v>436</v>
+      </c>
+      <c r="D143" t="s">
+        <v>805</v>
+      </c>
+      <c r="E143" t="s">
+        <v>806</v>
+      </c>
+      <c r="F143" t="s">
+        <v>439</v>
+      </c>
+      <c r="G143" t="s">
+        <v>442</v>
+      </c>
+      <c r="H143" t="s">
+        <v>436</v>
+      </c>
+      <c r="I143" t="s">
+        <v>807</v>
+      </c>
+      <c r="J143" t="s">
+        <v>808</v>
+      </c>
+      <c r="K143" t="s">
+        <v>465</v>
+      </c>
+      <c r="L143" t="s">
+        <v>436</v>
+      </c>
+      <c r="M143" t="s">
+        <v>442</v>
+      </c>
+      <c r="N143" t="s">
+        <v>443</v>
+      </c>
+      <c r="O143" t="s">
+        <v>451</v>
+      </c>
+      <c r="P143" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="144" spans="2:17">
+      <c r="B144" t="s">
+        <v>810</v>
+      </c>
+      <c r="C144" t="s">
+        <v>436</v>
+      </c>
+      <c r="D144" t="s">
+        <v>811</v>
+      </c>
+      <c r="E144" t="s">
+        <v>812</v>
+      </c>
+      <c r="F144" t="s">
+        <v>439</v>
+      </c>
+      <c r="G144" t="s">
+        <v>442</v>
+      </c>
+      <c r="H144" t="s">
+        <v>436</v>
+      </c>
+      <c r="I144" t="s">
+        <v>450</v>
+      </c>
+      <c r="J144" t="s">
+        <v>441</v>
+      </c>
+      <c r="K144" t="s">
+        <v>436</v>
+      </c>
+      <c r="L144" t="s">
+        <v>436</v>
+      </c>
+      <c r="M144" t="s">
+        <v>442</v>
+      </c>
+      <c r="N144" t="s">
+        <v>443</v>
+      </c>
+      <c r="O144" t="s">
+        <v>450</v>
+      </c>
+      <c r="P144" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="145" spans="2:17">
+      <c r="B145" t="s">
+        <v>814</v>
+      </c>
+      <c r="C145" t="s">
+        <v>436</v>
+      </c>
+      <c r="D145" t="s">
+        <v>815</v>
+      </c>
+      <c r="E145" t="s">
+        <v>816</v>
+      </c>
+      <c r="F145" t="s">
+        <v>439</v>
+      </c>
+      <c r="G145" t="s">
+        <v>442</v>
+      </c>
+      <c r="H145" t="s">
+        <v>817</v>
+      </c>
+      <c r="I145" t="s">
+        <v>807</v>
+      </c>
+      <c r="J145" t="s">
+        <v>818</v>
+      </c>
+      <c r="K145" t="s">
+        <v>450</v>
+      </c>
+      <c r="L145" t="s">
+        <v>436</v>
+      </c>
+      <c r="M145" t="s">
+        <v>442</v>
+      </c>
+      <c r="N145" t="s">
+        <v>443</v>
+      </c>
+      <c r="O145" t="s">
+        <v>451</v>
+      </c>
+      <c r="P145" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="147" spans="2:17">
+      <c r="B147" t="s">
+        <v>820</v>
+      </c>
+      <c r="C147" t="s">
+        <v>436</v>
+      </c>
+      <c r="D147" t="s">
+        <v>821</v>
+      </c>
+      <c r="E147" t="s">
+        <v>822</v>
+      </c>
+      <c r="F147" t="s">
+        <v>439</v>
+      </c>
+      <c r="G147" t="s">
+        <v>442</v>
+      </c>
+      <c r="H147" t="s">
+        <v>436</v>
+      </c>
+      <c r="I147" t="s">
+        <v>562</v>
+      </c>
+      <c r="J147" t="s">
+        <v>441</v>
+      </c>
+      <c r="K147" t="s">
+        <v>436</v>
+      </c>
+      <c r="L147" t="s">
+        <v>436</v>
+      </c>
+      <c r="M147" t="s">
+        <v>442</v>
+      </c>
+      <c r="N147" t="s">
+        <v>443</v>
+      </c>
+      <c r="O147" t="s">
+        <v>450</v>
+      </c>
+      <c r="P147" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="148" spans="2:17">
+      <c r="B148" t="s">
+        <v>824</v>
+      </c>
+      <c r="C148" t="s">
+        <v>436</v>
+      </c>
+      <c r="D148" t="s">
+        <v>825</v>
+      </c>
+      <c r="E148" t="s">
+        <v>826</v>
+      </c>
+      <c r="F148" t="s">
+        <v>439</v>
+      </c>
+      <c r="G148" t="s">
+        <v>442</v>
+      </c>
+      <c r="H148" t="s">
+        <v>436</v>
+      </c>
+      <c r="I148" t="s">
+        <v>827</v>
+      </c>
+      <c r="J148" t="s">
+        <v>441</v>
+      </c>
+      <c r="K148" t="s">
+        <v>436</v>
+      </c>
+      <c r="L148" t="s">
+        <v>436</v>
+      </c>
+      <c r="M148" t="s">
+        <v>442</v>
+      </c>
+      <c r="N148" t="s">
+        <v>443</v>
+      </c>
+      <c r="O148" t="s">
+        <v>562</v>
+      </c>
+      <c r="P148" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="149" spans="2:17">
+      <c r="B149" t="s">
+        <v>829</v>
+      </c>
+      <c r="C149" t="s">
+        <v>436</v>
+      </c>
+      <c r="D149" t="s">
+        <v>830</v>
+      </c>
+      <c r="E149" t="s">
+        <v>831</v>
+      </c>
+      <c r="F149" t="s">
+        <v>439</v>
+      </c>
+      <c r="G149" t="s">
+        <v>442</v>
+      </c>
+      <c r="H149" t="s">
+        <v>436</v>
+      </c>
+      <c r="I149" t="s">
+        <v>450</v>
+      </c>
+      <c r="J149" t="s">
+        <v>441</v>
+      </c>
+      <c r="K149" t="s">
+        <v>436</v>
+      </c>
+      <c r="L149" t="s">
+        <v>436</v>
+      </c>
+      <c r="M149" t="s">
+        <v>442</v>
+      </c>
+      <c r="N149" t="s">
+        <v>443</v>
+      </c>
+      <c r="O149" t="s">
+        <v>450</v>
+      </c>
+      <c r="P149" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="151" spans="2:17">
+      <c r="B151" t="s">
+        <v>833</v>
+      </c>
+      <c r="C151" t="s">
+        <v>436</v>
+      </c>
+      <c r="D151" t="s">
+        <v>834</v>
+      </c>
+      <c r="E151" t="s">
+        <v>835</v>
+      </c>
+      <c r="F151" t="s">
+        <v>439</v>
+      </c>
+      <c r="G151" t="s">
+        <v>442</v>
+      </c>
+      <c r="H151" t="s">
+        <v>436</v>
+      </c>
+      <c r="I151" t="s">
+        <v>555</v>
+      </c>
+      <c r="J151" t="s">
+        <v>441</v>
+      </c>
+      <c r="K151" t="s">
+        <v>436</v>
+      </c>
+      <c r="L151" t="s">
+        <v>436</v>
+      </c>
+      <c r="M151" t="s">
+        <v>442</v>
+      </c>
+      <c r="N151" t="s">
+        <v>443</v>
+      </c>
+      <c r="O151" t="s">
+        <v>450</v>
+      </c>
+      <c r="P151" t="s">
+        <v>1091</v>
+      </c>
+      <c r="Q151" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="152" spans="2:17">
+      <c r="B152" t="s">
+        <v>837</v>
+      </c>
+      <c r="C152" t="s">
+        <v>436</v>
+      </c>
+      <c r="D152" t="s">
+        <v>838</v>
+      </c>
+      <c r="E152" t="s">
+        <v>839</v>
+      </c>
+      <c r="F152" t="s">
+        <v>439</v>
+      </c>
+      <c r="G152" t="s">
+        <v>442</v>
+      </c>
+      <c r="H152" t="s">
+        <v>436</v>
+      </c>
+      <c r="I152" t="s">
+        <v>450</v>
+      </c>
+      <c r="J152" t="s">
+        <v>441</v>
+      </c>
+      <c r="K152" t="s">
+        <v>436</v>
+      </c>
+      <c r="L152" t="s">
+        <v>436</v>
+      </c>
+      <c r="M152" t="s">
+        <v>442</v>
+      </c>
+      <c r="N152" t="s">
+        <v>443</v>
+      </c>
+      <c r="O152" t="s">
+        <v>450</v>
+      </c>
+      <c r="P152" t="s">
+        <v>1091</v>
+      </c>
+      <c r="Q152" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="153" spans="2:17">
+      <c r="B153" t="s">
+        <v>841</v>
+      </c>
+      <c r="C153" t="s">
+        <v>436</v>
+      </c>
+      <c r="D153" t="s">
+        <v>842</v>
+      </c>
+      <c r="E153" t="s">
+        <v>843</v>
+      </c>
+      <c r="F153" t="s">
+        <v>439</v>
+      </c>
+      <c r="G153" t="s">
+        <v>442</v>
+      </c>
+      <c r="H153" t="s">
+        <v>436</v>
+      </c>
+      <c r="I153" t="s">
+        <v>439</v>
+      </c>
+      <c r="J153" t="s">
+        <v>441</v>
+      </c>
+      <c r="K153" t="s">
+        <v>436</v>
+      </c>
+      <c r="L153" t="s">
+        <v>436</v>
+      </c>
+      <c r="M153" t="s">
+        <v>442</v>
+      </c>
+      <c r="N153" t="s">
+        <v>443</v>
+      </c>
+      <c r="O153" t="s">
+        <v>450</v>
+      </c>
+      <c r="P153" t="s">
+        <v>1091</v>
+      </c>
+      <c r="Q153" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="154" spans="2:17">
+      <c r="B154" t="s">
+        <v>845</v>
+      </c>
+      <c r="C154" t="s">
+        <v>436</v>
+      </c>
+      <c r="D154" t="s">
+        <v>846</v>
+      </c>
+      <c r="E154" t="s">
+        <v>847</v>
+      </c>
+      <c r="F154" t="s">
+        <v>439</v>
+      </c>
+      <c r="G154" t="s">
+        <v>442</v>
+      </c>
+      <c r="H154" t="s">
+        <v>436</v>
+      </c>
+      <c r="I154" t="s">
+        <v>450</v>
+      </c>
+      <c r="J154" t="s">
+        <v>441</v>
+      </c>
+      <c r="K154" t="s">
+        <v>436</v>
+      </c>
+      <c r="L154" t="s">
+        <v>436</v>
+      </c>
+      <c r="M154" t="s">
+        <v>442</v>
+      </c>
+      <c r="N154" t="s">
+        <v>443</v>
+      </c>
+      <c r="O154" t="s">
+        <v>450</v>
+      </c>
+      <c r="P154" t="s">
+        <v>1091</v>
+      </c>
+      <c r="Q154" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="155" spans="2:17">
+      <c r="B155" t="s">
+        <v>849</v>
+      </c>
+      <c r="C155" t="s">
+        <v>436</v>
+      </c>
+      <c r="D155" t="s">
+        <v>850</v>
+      </c>
+      <c r="E155" t="s">
+        <v>851</v>
+      </c>
+      <c r="F155" t="s">
+        <v>439</v>
+      </c>
+      <c r="G155" t="s">
+        <v>442</v>
+      </c>
+      <c r="H155" t="s">
+        <v>436</v>
+      </c>
+      <c r="I155" t="s">
+        <v>562</v>
+      </c>
+      <c r="J155" t="s">
+        <v>441</v>
+      </c>
+      <c r="K155" t="s">
+        <v>436</v>
+      </c>
+      <c r="L155" t="s">
+        <v>436</v>
+      </c>
+      <c r="M155" t="s">
+        <v>442</v>
+      </c>
+      <c r="N155" t="s">
+        <v>443</v>
+      </c>
+      <c r="O155" t="s">
+        <v>450</v>
+      </c>
+      <c r="P155" t="s">
+        <v>1091</v>
+      </c>
+      <c r="Q155" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="157" spans="2:17">
+      <c r="B157" t="s">
+        <v>853</v>
+      </c>
+      <c r="C157" t="s">
+        <v>436</v>
+      </c>
+      <c r="D157" t="s">
+        <v>854</v>
+      </c>
+      <c r="E157" t="s">
+        <v>855</v>
+      </c>
+      <c r="F157" t="s">
+        <v>439</v>
+      </c>
+      <c r="G157" t="s">
+        <v>442</v>
+      </c>
+      <c r="H157" t="s">
+        <v>436</v>
+      </c>
+      <c r="I157" t="s">
+        <v>555</v>
+      </c>
+      <c r="J157" t="s">
+        <v>441</v>
+      </c>
+      <c r="K157" t="s">
+        <v>436</v>
+      </c>
+      <c r="L157" t="s">
+        <v>436</v>
+      </c>
+      <c r="M157" t="s">
+        <v>442</v>
+      </c>
+      <c r="N157" t="s">
+        <v>443</v>
+      </c>
+      <c r="O157" t="s">
+        <v>450</v>
+      </c>
+      <c r="P157" t="s">
+        <v>1091</v>
+      </c>
+      <c r="Q157" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="158" spans="2:17">
+      <c r="B158" t="s">
+        <v>857</v>
+      </c>
+      <c r="C158" t="s">
+        <v>436</v>
+      </c>
+      <c r="D158" t="s">
+        <v>858</v>
+      </c>
+      <c r="E158" t="s">
+        <v>859</v>
+      </c>
+      <c r="F158" t="s">
+        <v>439</v>
+      </c>
+      <c r="G158" t="s">
+        <v>442</v>
+      </c>
+      <c r="H158" t="s">
+        <v>436</v>
+      </c>
+      <c r="I158" t="s">
+        <v>450</v>
+      </c>
+      <c r="J158" t="s">
+        <v>441</v>
+      </c>
+      <c r="K158" t="s">
+        <v>436</v>
+      </c>
+      <c r="L158" t="s">
+        <v>436</v>
+      </c>
+      <c r="M158" t="s">
+        <v>442</v>
+      </c>
+      <c r="N158" t="s">
+        <v>443</v>
+      </c>
+      <c r="O158" t="s">
+        <v>450</v>
+      </c>
+      <c r="P158" t="s">
+        <v>1091</v>
+      </c>
+      <c r="Q158" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="159" spans="2:17">
+      <c r="B159" t="s">
+        <v>861</v>
+      </c>
+      <c r="C159" t="s">
+        <v>436</v>
+      </c>
+      <c r="D159" t="s">
+        <v>862</v>
+      </c>
+      <c r="E159" t="s">
+        <v>863</v>
+      </c>
+      <c r="F159" t="s">
+        <v>439</v>
+      </c>
+      <c r="G159" t="s">
+        <v>442</v>
+      </c>
+      <c r="H159" t="s">
+        <v>436</v>
+      </c>
+      <c r="I159" t="s">
+        <v>439</v>
+      </c>
+      <c r="J159" t="s">
+        <v>441</v>
+      </c>
+      <c r="K159" t="s">
+        <v>436</v>
+      </c>
+      <c r="L159" t="s">
+        <v>436</v>
+      </c>
+      <c r="M159" t="s">
+        <v>442</v>
+      </c>
+      <c r="N159" t="s">
+        <v>443</v>
+      </c>
+      <c r="O159" t="s">
+        <v>450</v>
+      </c>
+      <c r="P159" t="s">
+        <v>1091</v>
+      </c>
+      <c r="Q159" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="160" spans="2:17">
+      <c r="B160" t="s">
+        <v>865</v>
+      </c>
+      <c r="C160" t="s">
+        <v>436</v>
+      </c>
+      <c r="D160" t="s">
+        <v>866</v>
+      </c>
+      <c r="E160" t="s">
+        <v>867</v>
+      </c>
+      <c r="F160" t="s">
+        <v>439</v>
+      </c>
+      <c r="G160" t="s">
+        <v>442</v>
+      </c>
+      <c r="H160" t="s">
+        <v>436</v>
+      </c>
+      <c r="I160" t="s">
+        <v>450</v>
+      </c>
+      <c r="J160" t="s">
+        <v>441</v>
+      </c>
+      <c r="K160" t="s">
+        <v>436</v>
+      </c>
+      <c r="L160" t="s">
+        <v>436</v>
+      </c>
+      <c r="M160" t="s">
+        <v>442</v>
+      </c>
+      <c r="N160" t="s">
+        <v>443</v>
+      </c>
+      <c r="O160" t="s">
+        <v>450</v>
+      </c>
+      <c r="P160" t="s">
+        <v>1091</v>
+      </c>
+      <c r="Q160" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="161" spans="1:17">
+      <c r="B161" t="s">
+        <v>869</v>
+      </c>
+      <c r="C161" t="s">
+        <v>436</v>
+      </c>
+      <c r="D161" t="s">
+        <v>870</v>
+      </c>
+      <c r="E161" t="s">
+        <v>871</v>
+      </c>
+      <c r="F161" t="s">
+        <v>439</v>
+      </c>
+      <c r="G161" t="s">
+        <v>442</v>
+      </c>
+      <c r="H161" t="s">
+        <v>436</v>
+      </c>
+      <c r="I161" t="s">
+        <v>562</v>
+      </c>
+      <c r="J161" t="s">
+        <v>441</v>
+      </c>
+      <c r="K161" t="s">
+        <v>436</v>
+      </c>
+      <c r="L161" t="s">
+        <v>436</v>
+      </c>
+      <c r="M161" t="s">
+        <v>442</v>
+      </c>
+      <c r="N161" t="s">
+        <v>443</v>
+      </c>
+      <c r="O161" t="s">
+        <v>450</v>
+      </c>
+      <c r="P161" t="s">
+        <v>1091</v>
+      </c>
+      <c r="Q161" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="163" spans="1:17">
+      <c r="B163" t="s">
+        <v>873</v>
+      </c>
+      <c r="C163" t="s">
+        <v>436</v>
+      </c>
+      <c r="D163" t="s">
+        <v>874</v>
+      </c>
+      <c r="E163" t="s">
+        <v>875</v>
+      </c>
+      <c r="F163" t="s">
+        <v>439</v>
+      </c>
+      <c r="G163" t="s">
+        <v>442</v>
+      </c>
+      <c r="H163" t="s">
+        <v>436</v>
+      </c>
+      <c r="I163" t="s">
+        <v>555</v>
+      </c>
+      <c r="J163" t="s">
+        <v>441</v>
+      </c>
+      <c r="K163" t="s">
+        <v>436</v>
+      </c>
+      <c r="L163" t="s">
+        <v>436</v>
+      </c>
+      <c r="M163" t="s">
+        <v>442</v>
+      </c>
+      <c r="N163" t="s">
+        <v>443</v>
+      </c>
+      <c r="O163" t="s">
+        <v>450</v>
+      </c>
+      <c r="P163" t="s">
+        <v>1091</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="164" spans="1:17">
+      <c r="B164" t="s">
+        <v>877</v>
+      </c>
+      <c r="C164" t="s">
+        <v>436</v>
+      </c>
+      <c r="D164" t="s">
+        <v>878</v>
+      </c>
+      <c r="E164" t="s">
+        <v>879</v>
+      </c>
+      <c r="F164" t="s">
+        <v>439</v>
+      </c>
+      <c r="G164" t="s">
+        <v>442</v>
+      </c>
+      <c r="H164" t="s">
+        <v>436</v>
+      </c>
+      <c r="I164" t="s">
+        <v>450</v>
+      </c>
+      <c r="J164" t="s">
+        <v>441</v>
+      </c>
+      <c r="K164" t="s">
+        <v>436</v>
+      </c>
+      <c r="L164" t="s">
+        <v>436</v>
+      </c>
+      <c r="M164" t="s">
+        <v>442</v>
+      </c>
+      <c r="N164" t="s">
+        <v>443</v>
+      </c>
+      <c r="O164" t="s">
+        <v>450</v>
+      </c>
+      <c r="P164" t="s">
+        <v>1091</v>
+      </c>
+      <c r="Q164" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="165" spans="1:17">
+      <c r="B165" t="s">
+        <v>881</v>
+      </c>
+      <c r="C165" t="s">
+        <v>436</v>
+      </c>
+      <c r="D165" t="s">
+        <v>882</v>
+      </c>
+      <c r="E165" t="s">
+        <v>883</v>
+      </c>
+      <c r="F165" t="s">
+        <v>439</v>
+      </c>
+      <c r="G165" t="s">
+        <v>442</v>
+      </c>
+      <c r="H165" t="s">
+        <v>436</v>
+      </c>
+      <c r="I165" t="s">
+        <v>439</v>
+      </c>
+      <c r="J165" t="s">
+        <v>441</v>
+      </c>
+      <c r="K165" t="s">
+        <v>436</v>
+      </c>
+      <c r="L165" t="s">
+        <v>436</v>
+      </c>
+      <c r="M165" t="s">
+        <v>442</v>
+      </c>
+      <c r="N165" t="s">
+        <v>443</v>
+      </c>
+      <c r="O165" t="s">
+        <v>450</v>
+      </c>
+      <c r="P165" t="s">
+        <v>1091</v>
+      </c>
+      <c r="Q165" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="166" spans="1:17">
+      <c r="B166" t="s">
+        <v>885</v>
+      </c>
+      <c r="C166" t="s">
+        <v>436</v>
+      </c>
+      <c r="D166" t="s">
+        <v>886</v>
+      </c>
+      <c r="E166" t="s">
+        <v>887</v>
+      </c>
+      <c r="F166" t="s">
+        <v>439</v>
+      </c>
+      <c r="G166" t="s">
+        <v>442</v>
+      </c>
+      <c r="H166" t="s">
+        <v>436</v>
+      </c>
+      <c r="I166" t="s">
+        <v>450</v>
+      </c>
+      <c r="J166" t="s">
+        <v>441</v>
+      </c>
+      <c r="K166" t="s">
+        <v>436</v>
+      </c>
+      <c r="L166" t="s">
+        <v>436</v>
+      </c>
+      <c r="M166" t="s">
+        <v>442</v>
+      </c>
+      <c r="N166" t="s">
+        <v>443</v>
+      </c>
+      <c r="O166" t="s">
+        <v>450</v>
+      </c>
+      <c r="P166" t="s">
+        <v>1091</v>
+      </c>
+      <c r="Q166" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="167" spans="1:17">
+      <c r="B167" t="s">
+        <v>889</v>
+      </c>
+      <c r="C167" t="s">
+        <v>436</v>
+      </c>
+      <c r="D167" t="s">
+        <v>890</v>
+      </c>
+      <c r="E167" t="s">
+        <v>891</v>
+      </c>
+      <c r="F167" t="s">
+        <v>439</v>
+      </c>
+      <c r="G167" t="s">
+        <v>442</v>
+      </c>
+      <c r="H167" t="s">
+        <v>436</v>
+      </c>
+      <c r="I167" t="s">
+        <v>562</v>
+      </c>
+      <c r="J167" t="s">
+        <v>441</v>
+      </c>
+      <c r="K167" t="s">
+        <v>436</v>
+      </c>
+      <c r="L167" t="s">
+        <v>436</v>
+      </c>
+      <c r="M167" t="s">
+        <v>442</v>
+      </c>
+      <c r="N167" t="s">
+        <v>443</v>
+      </c>
+      <c r="O167" t="s">
+        <v>450</v>
+      </c>
+      <c r="P167" t="s">
+        <v>1091</v>
+      </c>
+      <c r="Q167" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="168" spans="1:17">
+      <c r="A168" t="s">
+        <v>700</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/LTD_DISPLAY_CPU3/readme/LTD故障代码表.xlsx
+++ b/LTD_DISPLAY_CPU3/readme/LTD故障代码表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="4"/>
+    <workbookView windowHeight="17655" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="总表" sheetId="1" r:id="rId1"/>
@@ -13074,7 +13074,7 @@
         <v>450</v>
       </c>
       <c r="P64" t="s">
-        <v>441</v>
+        <v>712</v>
       </c>
       <c r="Q64" t="s">
         <v>845</v>

--- a/LTD_DISPLAY_CPU3/readme/LTD故障代码表.xlsx
+++ b/LTD_DISPLAY_CPU3/readme/LTD故障代码表.xlsx
@@ -4070,6 +4070,9 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -13511,8 +13514,8 @@
       <c r="K74" t="s">
         <v>450</v>
       </c>
-      <c r="L74" t="s">
-        <v>436</v>
+      <c r="L74" s="19" t="s">
+        <v>553</v>
       </c>
       <c r="M74" t="s">
         <v>442</v>
@@ -13561,8 +13564,8 @@
       <c r="K75" t="s">
         <v>450</v>
       </c>
-      <c r="L75" t="s">
-        <v>436</v>
+      <c r="L75" s="19" t="s">
+        <v>560</v>
       </c>
       <c r="M75" t="s">
         <v>442</v>
@@ -14409,7 +14412,7 @@
         <v>516</v>
       </c>
       <c r="K94" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="L94" t="s">
         <v>436</v>
@@ -14459,7 +14462,7 @@
         <v>516</v>
       </c>
       <c r="K95" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="L95" t="s">
         <v>436</v>
@@ -14509,7 +14512,7 @@
         <v>516</v>
       </c>
       <c r="K96" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="L96" t="s">
         <v>436</v>
@@ -14559,7 +14562,7 @@
         <v>516</v>
       </c>
       <c r="K97" t="s">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="L97" t="s">
         <v>436</v>

--- a/LTD_DISPLAY_CPU3/readme/LTD故障代码表.xlsx
+++ b/LTD_DISPLAY_CPU3/readme/LTD故障代码表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="4"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="总表" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4008" uniqueCount="1093">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4008" uniqueCount="1094">
   <si>
     <t>故障类型</t>
   </si>
@@ -2463,28 +2463,34 @@
     <t>(uint8_t*)"HysTh"},</t>
   </si>
   <si>
-    <t>{(uint8_t*)"保留12",</t>
-  </si>
-  <si>
-    <t>COM_NUM_DEVICEPARAM_RESERVED12,</t>
-  </si>
-  <si>
-    <t>HOLDREGISTER_DEVICEPARAM_RESERVED12,</t>
-  </si>
-  <si>
-    <t>(uint8_t*)"Rsv12"},</t>
-  </si>
-  <si>
-    <t>{(uint8_t*)"保留13",</t>
-  </si>
-  <si>
-    <t>COM_NUM_DEVICEPARAM_RESERVED13,</t>
-  </si>
-  <si>
-    <t>HOLDREGISTER_DEVICEPARAM_RESERVED13,</t>
-  </si>
-  <si>
-    <t>(uint8_t*)"Rsv13"},</t>
+    <t>{(uint8_t*)"液位跟随频率",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_OILLEVEL_FREQUENCY,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_OILLEVEL_FREQUENCY,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"HZ",</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"FollowFreq"},</t>
+  </si>
+  <si>
+    <t>{(uint8_t*)"液位跟随密度",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_OILLEVEL_DENSITY,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_OILLEVEL_DENSITY,</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"kg/m3",</t>
+  </si>
+  <si>
+    <t>(uint8_t*)"FollowDens"},</t>
   </si>
   <si>
     <t>{(uint8_t*)"水位罐高",</t>
@@ -3055,9 +3061,6 @@
   </si>
   <si>
     <t>2000,</t>
-  </si>
-  <si>
-    <t>(uint8_t*)"kg/m3",</t>
   </si>
   <si>
     <t>(uint8_t*)"InD"},</t>
@@ -4070,9 +4073,6 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -12527,7 +12527,7 @@
         <v>450</v>
       </c>
       <c r="P51" t="s">
-        <v>441</v>
+        <v>712</v>
       </c>
       <c r="Q51" t="s">
         <v>642</v>
@@ -12559,7 +12559,7 @@
         <v>436</v>
       </c>
       <c r="J52" t="s">
-        <v>441</v>
+        <v>813</v>
       </c>
       <c r="K52" t="s">
         <v>436</v>
@@ -12568,33 +12568,33 @@
         <v>436</v>
       </c>
       <c r="M52" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N52" t="s">
         <v>443</v>
       </c>
       <c r="O52" t="s">
-        <v>444</v>
+        <v>562</v>
       </c>
       <c r="P52" t="s">
         <v>441</v>
       </c>
       <c r="Q52" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="53" spans="2:17">
       <c r="B53" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C53" t="s">
         <v>436</v>
       </c>
       <c r="D53" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="E53" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="F53" t="s">
         <v>439</v>
@@ -12609,42 +12609,42 @@
         <v>436</v>
       </c>
       <c r="J53" t="s">
-        <v>441</v>
+        <v>818</v>
       </c>
       <c r="K53" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="L53" t="s">
         <v>436</v>
       </c>
       <c r="M53" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N53" t="s">
         <v>443</v>
       </c>
       <c r="O53" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="P53" t="s">
         <v>441</v>
       </c>
       <c r="Q53" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="55" spans="2:17">
       <c r="B55" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="C55" t="s">
         <v>436</v>
       </c>
       <c r="D55" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="E55" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="F55" t="s">
         <v>439</v>
@@ -12680,21 +12680,21 @@
         <v>441</v>
       </c>
       <c r="Q55" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
     </row>
     <row r="56" spans="2:17">
       <c r="B56" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="C56" t="s">
         <v>436</v>
       </c>
       <c r="D56" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="E56" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="F56" t="s">
         <v>439</v>
@@ -12730,7 +12730,7 @@
         <v>441</v>
       </c>
       <c r="Q56" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
     </row>
     <row r="57" spans="2:17">
@@ -12785,16 +12785,16 @@
     </row>
     <row r="58" spans="2:17">
       <c r="B58" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="C58" t="s">
         <v>436</v>
       </c>
       <c r="D58" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="E58" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="F58" t="s">
         <v>439</v>
@@ -12830,21 +12830,21 @@
         <v>441</v>
       </c>
       <c r="Q58" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
     </row>
     <row r="59" spans="2:17">
       <c r="B59" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="C59" t="s">
         <v>436</v>
       </c>
       <c r="D59" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="E59" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="F59" t="s">
         <v>439</v>
@@ -12880,7 +12880,7 @@
         <v>441</v>
       </c>
       <c r="Q59" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
     </row>
     <row r="60" spans="2:17">
@@ -12935,16 +12935,16 @@
     </row>
     <row r="61" spans="2:17">
       <c r="B61" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="C61" t="s">
         <v>436</v>
       </c>
       <c r="D61" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="E61" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="F61" t="s">
         <v>439</v>
@@ -12980,21 +12980,21 @@
         <v>441</v>
       </c>
       <c r="Q61" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
     </row>
     <row r="62" spans="2:17">
       <c r="B62" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="C62" t="s">
         <v>436</v>
       </c>
       <c r="D62" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="E62" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="F62" t="s">
         <v>439</v>
@@ -13030,21 +13030,21 @@
         <v>441</v>
       </c>
       <c r="Q62" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
     </row>
     <row r="64" spans="2:17">
       <c r="B64" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C64" t="s">
         <v>436</v>
       </c>
       <c r="D64" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="E64" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="F64" t="s">
         <v>439</v>
@@ -13080,21 +13080,21 @@
         <v>712</v>
       </c>
       <c r="Q64" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
     </row>
     <row r="65" spans="2:17">
       <c r="B65" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C65" t="s">
         <v>436</v>
       </c>
       <c r="D65" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="E65" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="F65" t="s">
         <v>439</v>
@@ -13130,21 +13130,21 @@
         <v>441</v>
       </c>
       <c r="Q65" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
     </row>
     <row r="66" spans="2:17">
       <c r="B66" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="C66" t="s">
         <v>436</v>
       </c>
       <c r="D66" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="E66" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="F66" t="s">
         <v>439</v>
@@ -13180,7 +13180,7 @@
         <v>441</v>
       </c>
       <c r="Q66" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
     </row>
     <row r="67" spans="2:17">
@@ -13191,10 +13191,10 @@
         <v>436</v>
       </c>
       <c r="D67" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="E67" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="F67" t="s">
         <v>439</v>
@@ -13241,10 +13241,10 @@
         <v>436</v>
       </c>
       <c r="D68" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="E68" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="F68" t="s">
         <v>439</v>
@@ -13291,10 +13291,10 @@
         <v>436</v>
       </c>
       <c r="D69" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="E69" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="F69" t="s">
         <v>439</v>
@@ -13341,10 +13341,10 @@
         <v>436</v>
       </c>
       <c r="D70" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="E70" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="F70" t="s">
         <v>439</v>
@@ -13385,16 +13385,16 @@
     </row>
     <row r="71" spans="2:17">
       <c r="B71" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="C71" t="s">
         <v>436</v>
       </c>
       <c r="D71" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="E71" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="F71" t="s">
         <v>439</v>
@@ -13430,21 +13430,21 @@
         <v>441</v>
       </c>
       <c r="Q71" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
     </row>
     <row r="72" spans="2:17">
       <c r="B72" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="C72" t="s">
         <v>436</v>
       </c>
       <c r="D72" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="E72" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="F72" t="s">
         <v>439</v>
@@ -13480,12 +13480,12 @@
         <v>441</v>
       </c>
       <c r="Q72" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
     </row>
     <row r="74" spans="2:17">
       <c r="B74" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="C74" t="s">
         <v>436</v>
@@ -13514,7 +13514,7 @@
       <c r="K74" t="s">
         <v>450</v>
       </c>
-      <c r="L74" s="19" t="s">
+      <c r="L74" t="s">
         <v>553</v>
       </c>
       <c r="M74" t="s">
@@ -13535,7 +13535,7 @@
     </row>
     <row r="75" spans="2:17">
       <c r="B75" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="C75" t="s">
         <v>436</v>
@@ -13564,7 +13564,7 @@
       <c r="K75" t="s">
         <v>450</v>
       </c>
-      <c r="L75" s="19" t="s">
+      <c r="L75" t="s">
         <v>560</v>
       </c>
       <c r="M75" t="s">
@@ -13585,16 +13585,16 @@
     </row>
     <row r="76" spans="2:17">
       <c r="B76" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="C76" t="s">
         <v>436</v>
       </c>
       <c r="D76" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="E76" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="F76" t="s">
         <v>439</v>
@@ -13630,21 +13630,21 @@
         <v>441</v>
       </c>
       <c r="Q76" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
     </row>
     <row r="77" spans="2:17">
       <c r="B77" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="C77" t="s">
         <v>436</v>
       </c>
       <c r="D77" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="E77" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="F77" t="s">
         <v>439</v>
@@ -13680,7 +13680,7 @@
         <v>441</v>
       </c>
       <c r="Q77" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
     </row>
     <row r="79" spans="2:17">
@@ -14185,16 +14185,16 @@
     </row>
     <row r="89" spans="2:17">
       <c r="B89" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="C89" t="s">
         <v>436</v>
       </c>
       <c r="D89" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="E89" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="F89" t="s">
         <v>439</v>
@@ -14230,21 +14230,21 @@
         <v>441</v>
       </c>
       <c r="Q89" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
     </row>
     <row r="90" spans="2:17">
       <c r="B90" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="C90" t="s">
         <v>436</v>
       </c>
       <c r="D90" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="E90" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="F90" t="s">
         <v>439</v>
@@ -14280,21 +14280,21 @@
         <v>441</v>
       </c>
       <c r="Q90" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
     </row>
     <row r="91" spans="2:17">
       <c r="B91" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="C91" t="s">
         <v>436</v>
       </c>
       <c r="D91" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="E91" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="F91" t="s">
         <v>439</v>
@@ -14330,21 +14330,21 @@
         <v>441</v>
       </c>
       <c r="Q91" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="92" spans="2:17">
       <c r="B92" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="C92" t="s">
         <v>436</v>
       </c>
       <c r="D92" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="E92" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="F92" t="s">
         <v>439</v>
@@ -14380,21 +14380,21 @@
         <v>441</v>
       </c>
       <c r="Q92" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
     </row>
     <row r="94" spans="2:17">
       <c r="B94" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="C94" t="s">
         <v>436</v>
       </c>
       <c r="D94" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="E94" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="F94" t="s">
         <v>439</v>
@@ -14430,21 +14430,21 @@
         <v>441</v>
       </c>
       <c r="Q94" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
     </row>
     <row r="95" spans="2:17">
       <c r="B95" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="C95" t="s">
         <v>436</v>
       </c>
       <c r="D95" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="E95" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="F95" t="s">
         <v>439</v>
@@ -14480,21 +14480,21 @@
         <v>441</v>
       </c>
       <c r="Q95" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="96" spans="2:17">
       <c r="B96" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="C96" t="s">
         <v>436</v>
       </c>
       <c r="D96" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="E96" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="F96" t="s">
         <v>439</v>
@@ -14530,21 +14530,21 @@
         <v>441</v>
       </c>
       <c r="Q96" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
     </row>
     <row r="97" spans="2:17">
       <c r="B97" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="C97" t="s">
         <v>436</v>
       </c>
       <c r="D97" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="E97" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="F97" t="s">
         <v>439</v>
@@ -14580,21 +14580,21 @@
         <v>441</v>
       </c>
       <c r="Q97" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
     </row>
     <row r="98" spans="2:17">
       <c r="B98" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="C98" t="s">
         <v>436</v>
       </c>
       <c r="D98" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="E98" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="F98" t="s">
         <v>439</v>
@@ -14630,21 +14630,21 @@
         <v>441</v>
       </c>
       <c r="Q98" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
     </row>
     <row r="99" spans="2:17">
       <c r="B99" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="C99" t="s">
         <v>436</v>
       </c>
       <c r="D99" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="E99" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="F99" t="s">
         <v>439</v>
@@ -14680,7 +14680,7 @@
         <v>441</v>
       </c>
       <c r="Q99" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
     </row>
     <row r="101" spans="2:17">
@@ -14835,16 +14835,16 @@
     </row>
     <row r="104" spans="2:17">
       <c r="B104" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="C104" t="s">
         <v>436</v>
       </c>
       <c r="D104" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="E104" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="F104" t="s">
         <v>439</v>
@@ -14880,21 +14880,21 @@
         <v>441</v>
       </c>
       <c r="Q104" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
     </row>
     <row r="105" spans="2:17">
       <c r="B105" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="C105" t="s">
         <v>436</v>
       </c>
       <c r="D105" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="E105" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="F105" t="s">
         <v>439</v>
@@ -14930,7 +14930,7 @@
         <v>441</v>
       </c>
       <c r="Q105" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
     </row>
     <row r="107" spans="2:17">
@@ -15385,16 +15385,16 @@
     </row>
     <row r="116" spans="2:17">
       <c r="B116" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="C116" t="s">
         <v>436</v>
       </c>
       <c r="D116" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="E116" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="F116" t="s">
         <v>439</v>
@@ -15430,21 +15430,21 @@
         <v>441</v>
       </c>
       <c r="Q116" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
     </row>
     <row r="117" spans="2:17">
       <c r="B117" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="C117" t="s">
         <v>436</v>
       </c>
       <c r="D117" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="E117" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="F117" t="s">
         <v>439</v>
@@ -15480,18 +15480,18 @@
         <v>441</v>
       </c>
       <c r="Q117" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
     </row>
     <row r="119" spans="2:17">
       <c r="B119" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="C119" t="s">
         <v>436</v>
       </c>
       <c r="D119" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="E119" t="s">
         <v>521</v>
@@ -15535,7 +15535,7 @@
     </row>
     <row r="120" spans="2:17">
       <c r="B120" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="C120" t="s">
         <v>436</v>
@@ -15591,7 +15591,7 @@
         <v>436</v>
       </c>
       <c r="D121" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="E121" t="s">
         <v>532</v>
@@ -15641,7 +15641,7 @@
         <v>436</v>
       </c>
       <c r="D122" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="E122" t="s">
         <v>536</v>
@@ -15685,13 +15685,13 @@
     </row>
     <row r="123" spans="2:17">
       <c r="B123" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="C123" t="s">
         <v>436</v>
       </c>
       <c r="D123" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="E123" t="s">
         <v>540</v>
@@ -15730,7 +15730,7 @@
         <v>441</v>
       </c>
       <c r="Q123" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
     </row>
     <row r="124" spans="2:17">
@@ -15741,7 +15741,7 @@
         <v>436</v>
       </c>
       <c r="D124" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="E124" t="s">
         <v>544</v>
@@ -15780,21 +15780,21 @@
         <v>441</v>
       </c>
       <c r="Q124" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
     </row>
     <row r="125" spans="2:17">
       <c r="B125" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="C125" t="s">
         <v>436</v>
       </c>
       <c r="D125" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="E125" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="F125" t="s">
         <v>439</v>
@@ -15830,21 +15830,21 @@
         <v>441</v>
       </c>
       <c r="Q125" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
     </row>
     <row r="126" spans="2:17">
       <c r="B126" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="C126" t="s">
         <v>436</v>
       </c>
       <c r="D126" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="E126" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="F126" t="s">
         <v>439</v>
@@ -15880,21 +15880,21 @@
         <v>441</v>
       </c>
       <c r="Q126" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
     </row>
     <row r="129" spans="2:17">
       <c r="B129" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="C129" t="s">
         <v>436</v>
       </c>
       <c r="D129" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="E129" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="F129" t="s">
         <v>439</v>
@@ -15930,21 +15930,21 @@
         <v>441</v>
       </c>
       <c r="Q129" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
     </row>
     <row r="130" spans="2:17">
       <c r="B130" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="C130" t="s">
         <v>436</v>
       </c>
       <c r="D130" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="E130" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="F130" t="s">
         <v>439</v>
@@ -15980,21 +15980,21 @@
         <v>441</v>
       </c>
       <c r="Q130" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
     </row>
     <row r="131" spans="2:17">
       <c r="B131" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="C131" t="s">
         <v>436</v>
       </c>
       <c r="D131" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="E131" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="F131" t="s">
         <v>439</v>
@@ -16030,7 +16030,7 @@
         <v>441</v>
       </c>
       <c r="Q131" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
     </row>
     <row r="132" spans="2:17">
@@ -16085,12 +16085,12 @@
     </row>
     <row r="135" spans="2:17">
       <c r="B135" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
     </row>
     <row r="136" spans="2:17">
       <c r="B136" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="C136" t="s">
         <v>436</v>
@@ -16140,7 +16140,7 @@
     </row>
     <row r="137" spans="2:17">
       <c r="B137" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="C137" t="s">
         <v>436</v>
@@ -16190,13 +16190,13 @@
     </row>
     <row r="138" spans="2:17">
       <c r="B138" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="C138" t="s">
         <v>436</v>
       </c>
       <c r="D138" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="E138" t="s">
         <v>528</v>
@@ -16340,13 +16340,13 @@
     </row>
     <row r="141" spans="2:17">
       <c r="B141" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="C141" t="s">
         <v>436</v>
       </c>
       <c r="D141" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="E141" t="s">
         <v>540</v>
@@ -16385,7 +16385,7 @@
         <v>441</v>
       </c>
       <c r="Q141" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
     </row>
     <row r="142" spans="2:17">
@@ -16435,7 +16435,7 @@
         <v>441</v>
       </c>
       <c r="Q142" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
     </row>
     <row r="143" spans="2:17">
@@ -16485,7 +16485,7 @@
         <v>441</v>
       </c>
       <c r="Q143" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
     </row>
     <row r="144" spans="2:17">
@@ -16496,7 +16496,7 @@
         <v>436</v>
       </c>
       <c r="D144" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="E144" t="s">
         <v>544</v>
@@ -16535,7 +16535,7 @@
         <v>441</v>
       </c>
       <c r="Q144" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
     </row>
     <row r="145" spans="2:17">
@@ -16546,7 +16546,7 @@
         <v>436</v>
       </c>
       <c r="D145" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="E145" t="s">
         <v>544</v>
@@ -16585,26 +16585,26 @@
         <v>441</v>
       </c>
       <c r="Q145" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
     </row>
     <row r="147" spans="2:17">
       <c r="B147" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
     </row>
     <row r="148" spans="2:17">
       <c r="B148" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="C148" t="s">
         <v>436</v>
       </c>
       <c r="D148" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="E148" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="F148" t="s">
         <v>439</v>
@@ -16640,21 +16640,21 @@
         <v>441</v>
       </c>
       <c r="Q148" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
     </row>
     <row r="149" spans="2:17">
       <c r="B149" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="C149" t="s">
         <v>436</v>
       </c>
       <c r="D149" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="E149" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="F149" t="s">
         <v>439</v>
@@ -16690,21 +16690,21 @@
         <v>441</v>
       </c>
       <c r="Q149" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
     </row>
     <row r="151" spans="2:17">
       <c r="B151" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="C151" t="s">
         <v>436</v>
       </c>
       <c r="D151" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="E151" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="F151" t="s">
         <v>439</v>
@@ -16740,21 +16740,21 @@
         <v>441</v>
       </c>
       <c r="Q151" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
     </row>
     <row r="152" spans="2:17">
       <c r="B152" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="C152" t="s">
         <v>436</v>
       </c>
       <c r="D152" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="E152" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="F152" t="s">
         <v>439</v>
@@ -16790,21 +16790,21 @@
         <v>441</v>
       </c>
       <c r="Q152" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
     </row>
     <row r="153" spans="2:17">
       <c r="B153" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="C153" t="s">
         <v>436</v>
       </c>
       <c r="D153" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="E153" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="F153" t="s">
         <v>439</v>
@@ -16840,21 +16840,21 @@
         <v>441</v>
       </c>
       <c r="Q153" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
     </row>
     <row r="154" spans="2:17">
       <c r="B154" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="C154" t="s">
         <v>436</v>
       </c>
       <c r="D154" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="E154" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="F154" t="s">
         <v>439</v>
@@ -16890,21 +16890,21 @@
         <v>441</v>
       </c>
       <c r="Q154" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
     </row>
     <row r="156" spans="2:17">
       <c r="B156" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="C156" t="s">
         <v>436</v>
       </c>
       <c r="D156" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="E156" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="F156" t="s">
         <v>439</v>
@@ -16940,21 +16940,21 @@
         <v>441</v>
       </c>
       <c r="Q156" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="157" spans="2:17">
       <c r="B157" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="C157" t="s">
         <v>436</v>
       </c>
       <c r="D157" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="E157" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="F157" t="s">
         <v>439</v>
@@ -16990,21 +16990,21 @@
         <v>441</v>
       </c>
       <c r="Q157" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="158" spans="2:17">
       <c r="B158" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="C158" t="s">
         <v>436</v>
       </c>
       <c r="D158" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="E158" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="F158" t="s">
         <v>439</v>
@@ -17016,10 +17016,10 @@
         <v>436</v>
       </c>
       <c r="I158" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="J158" t="s">
-        <v>1008</v>
+        <v>818</v>
       </c>
       <c r="K158" t="s">
         <v>465</v>
@@ -17040,21 +17040,21 @@
         <v>441</v>
       </c>
       <c r="Q158" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="159" spans="2:17">
       <c r="B159" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="C159" t="s">
         <v>436</v>
       </c>
       <c r="D159" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="E159" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="F159" t="s">
         <v>439</v>
@@ -17090,21 +17090,21 @@
         <v>441</v>
       </c>
       <c r="Q159" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="160" spans="2:17">
       <c r="B160" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="C160" t="s">
         <v>436</v>
       </c>
       <c r="D160" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E160" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="F160" t="s">
         <v>439</v>
@@ -17113,13 +17113,13 @@
         <v>442</v>
       </c>
       <c r="H160" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="I160" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="J160" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="K160" t="s">
         <v>450</v>
@@ -17140,21 +17140,21 @@
         <v>441</v>
       </c>
       <c r="Q160" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="162" spans="2:17">
       <c r="B162" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="C162" t="s">
         <v>436</v>
       </c>
       <c r="D162" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="E162" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="F162" t="s">
         <v>439</v>
@@ -17190,21 +17190,21 @@
         <v>441</v>
       </c>
       <c r="Q162" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="163" spans="2:17">
       <c r="B163" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="C163" t="s">
         <v>436</v>
       </c>
       <c r="D163" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="E163" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="F163" t="s">
         <v>439</v>
@@ -17216,7 +17216,7 @@
         <v>436</v>
       </c>
       <c r="I163" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="J163" t="s">
         <v>441</v>
@@ -17240,21 +17240,21 @@
         <v>441</v>
       </c>
       <c r="Q163" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="164" spans="2:17">
       <c r="B164" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="C164" t="s">
         <v>436</v>
       </c>
       <c r="D164" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="E164" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F164" t="s">
         <v>439</v>
@@ -17290,21 +17290,21 @@
         <v>441</v>
       </c>
       <c r="Q164" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="166" spans="2:17">
       <c r="B166" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="C166" t="s">
         <v>436</v>
       </c>
       <c r="D166" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="E166" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="F166" t="s">
         <v>439</v>
@@ -17340,21 +17340,21 @@
         <v>712</v>
       </c>
       <c r="Q166" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="167" spans="2:17">
       <c r="B167" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="C167" t="s">
         <v>436</v>
       </c>
       <c r="D167" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="E167" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F167" t="s">
         <v>439</v>
@@ -17390,21 +17390,21 @@
         <v>712</v>
       </c>
       <c r="Q167" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="168" spans="2:17">
       <c r="B168" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C168" t="s">
         <v>436</v>
       </c>
       <c r="D168" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="E168" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="F168" t="s">
         <v>439</v>
@@ -17440,21 +17440,21 @@
         <v>712</v>
       </c>
       <c r="Q168" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="169" spans="2:17">
       <c r="B169" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C169" t="s">
         <v>436</v>
       </c>
       <c r="D169" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="E169" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="F169" t="s">
         <v>439</v>
@@ -17490,21 +17490,21 @@
         <v>712</v>
       </c>
       <c r="Q169" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="170" spans="2:17">
       <c r="B170" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="C170" t="s">
         <v>436</v>
       </c>
       <c r="D170" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="E170" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="F170" t="s">
         <v>439</v>
@@ -17540,21 +17540,21 @@
         <v>712</v>
       </c>
       <c r="Q170" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="172" spans="2:17">
       <c r="B172" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="C172" t="s">
         <v>436</v>
       </c>
       <c r="D172" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="E172" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="F172" t="s">
         <v>439</v>
@@ -17590,21 +17590,21 @@
         <v>712</v>
       </c>
       <c r="Q172" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="173" spans="2:17">
       <c r="B173" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C173" t="s">
         <v>436</v>
       </c>
       <c r="D173" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="E173" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="F173" t="s">
         <v>439</v>
@@ -17640,21 +17640,21 @@
         <v>712</v>
       </c>
       <c r="Q173" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="174" spans="2:17">
       <c r="B174" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="C174" t="s">
         <v>436</v>
       </c>
       <c r="D174" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="E174" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="F174" t="s">
         <v>439</v>
@@ -17690,21 +17690,21 @@
         <v>712</v>
       </c>
       <c r="Q174" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="175" spans="2:17">
       <c r="B175" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C175" t="s">
         <v>436</v>
       </c>
       <c r="D175" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="E175" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="F175" t="s">
         <v>439</v>
@@ -17740,21 +17740,21 @@
         <v>712</v>
       </c>
       <c r="Q175" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="176" spans="2:17">
       <c r="B176" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="C176" t="s">
         <v>436</v>
       </c>
       <c r="D176" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="E176" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="F176" t="s">
         <v>439</v>
@@ -17790,21 +17790,21 @@
         <v>712</v>
       </c>
       <c r="Q176" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="178" spans="1:17">
       <c r="B178" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="C178" t="s">
         <v>436</v>
       </c>
       <c r="D178" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="E178" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="F178" t="s">
         <v>439</v>
@@ -17840,21 +17840,21 @@
         <v>712</v>
       </c>
       <c r="Q178" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="179" spans="1:17">
       <c r="B179" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C179" t="s">
         <v>436</v>
       </c>
       <c r="D179" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="E179" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="F179" t="s">
         <v>439</v>
@@ -17890,21 +17890,21 @@
         <v>712</v>
       </c>
       <c r="Q179" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="180" spans="1:17">
       <c r="B180" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="C180" t="s">
         <v>436</v>
       </c>
       <c r="D180" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="E180" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F180" t="s">
         <v>439</v>
@@ -17940,21 +17940,21 @@
         <v>712</v>
       </c>
       <c r="Q180" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="181" spans="1:17">
       <c r="B181" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="C181" t="s">
         <v>436</v>
       </c>
       <c r="D181" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="E181" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="F181" t="s">
         <v>439</v>
@@ -17990,21 +17990,21 @@
         <v>712</v>
       </c>
       <c r="Q181" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="182" spans="1:17">
       <c r="B182" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="C182" t="s">
         <v>436</v>
       </c>
       <c r="D182" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="E182" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="F182" t="s">
         <v>439</v>
@@ -18040,7 +18040,7 @@
         <v>712</v>
       </c>
       <c r="Q182" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="183" spans="1:17">

--- a/LTD_DISPLAY_CPU3/readme/LTD故障代码表.xlsx
+++ b/LTD_DISPLAY_CPU3/readme/LTD故障代码表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="4"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="总表" sheetId="1" r:id="rId1"/>
@@ -2505,13 +2505,13 @@
     <t>(uint8_t*)"WaterTankH"},</t>
   </si>
   <si>
-    <t>{(uint8_t*)"水位探头距差",</t>
-  </si>
-  <si>
-    <t>COM_NUM_DEVICEPARAM_WATER_LEVEL_SENSOR_DISTANCE_DIFF,</t>
-  </si>
-  <si>
-    <t>HOLDREGISTER_DEVICEPARAM_WATER_LEVEL_SENSOR_DISTANCE_DIFF,</t>
+    <t>{(uint8_t*)"水位测量方式",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_WATER_LEVEL_MODE,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_WATER_LEVEL_MODE,</t>
   </si>
   <si>
     <t>(uint8_t*)"WaterSenDiff"},</t>
@@ -2553,13 +2553,13 @@
     <t>(uint8_t*)"ZeroCap"},</t>
   </si>
   <si>
-    <t>{(uint8_t*)"保留15",</t>
-  </si>
-  <si>
-    <t>COM_NUM_DEVICEPARAM_RESERVED15,</t>
-  </si>
-  <si>
-    <t>HOLDREGISTER_DEVICEPARAM_RESERVED15,</t>
+    <t>{(uint8_t*)"水位稳定阈值",</t>
+  </si>
+  <si>
+    <t>COM_NUM_DEVICEPARAM_WATER_STABLE_THRESHOLD,</t>
+  </si>
+  <si>
+    <t>HOLDREGISTER_DEVICEPARAM_WATER_STABLE_THRESHOLD,</t>
   </si>
   <si>
     <t>(uint8_t*)"Rsv15"},</t>
@@ -12703,28 +12703,28 @@
         <v>440</v>
       </c>
       <c r="H56" t="s">
-        <v>803</v>
+        <v>436</v>
       </c>
       <c r="I56" t="s">
-        <v>804</v>
+        <v>436</v>
       </c>
       <c r="J56" t="s">
-        <v>516</v>
+        <v>441</v>
       </c>
       <c r="K56" t="s">
+        <v>436</v>
+      </c>
+      <c r="L56" t="s">
+        <v>436</v>
+      </c>
+      <c r="M56" t="s">
+        <v>442</v>
+      </c>
+      <c r="N56" t="s">
+        <v>443</v>
+      </c>
+      <c r="O56" t="s">
         <v>450</v>
-      </c>
-      <c r="L56" t="s">
-        <v>436</v>
-      </c>
-      <c r="M56" t="s">
-        <v>442</v>
-      </c>
-      <c r="N56" t="s">
-        <v>443</v>
-      </c>
-      <c r="O56" t="s">
-        <v>451</v>
       </c>
       <c r="P56" t="s">
         <v>441</v>
@@ -12968,7 +12968,7 @@
         <v>436</v>
       </c>
       <c r="M61" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N61" t="s">
         <v>443</v>
@@ -13009,22 +13009,22 @@
         <v>436</v>
       </c>
       <c r="J62" t="s">
-        <v>441</v>
+        <v>516</v>
       </c>
       <c r="K62" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="L62" t="s">
         <v>436</v>
       </c>
       <c r="M62" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N62" t="s">
         <v>443</v>
       </c>
       <c r="O62" t="s">
-        <v>444</v>
+        <v>562</v>
       </c>
       <c r="P62" t="s">
         <v>441</v>
